--- a/model/Outputs/11. Interest rate/40/Output Files/0.1/Output_9_40.xlsx
+++ b/model/Outputs/11. Interest rate/40/Output Files/0.1/Output_9_40.xlsx
@@ -496,7 +496,7 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>4438133.407212844</v>
+        <v>4478083.848167944</v>
       </c>
     </row>
     <row r="7">
@@ -506,7 +506,7 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>6764066.2454583</v>
+        <v>6764066.24545839</v>
       </c>
     </row>
     <row r="8">
@@ -516,7 +516,7 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>6764066.2454583</v>
+        <v>6764066.24545839</v>
       </c>
     </row>
     <row r="9">
@@ -526,7 +526,7 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>3307259.142253605</v>
+        <v>3307259.142253737</v>
       </c>
     </row>
     <row r="10">
@@ -536,7 +536,7 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>3307259.142253605</v>
+        <v>3307259.142253737</v>
       </c>
     </row>
     <row r="11">
@@ -556,7 +556,7 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>48827438.17475404</v>
+        <v>48827438.174754</v>
       </c>
     </row>
   </sheetData>
@@ -654,7 +654,7 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>481.9993129555745</v>
+        <v>81.99931295557451</v>
       </c>
       <c r="C2" t="n">
         <v>49.47457824299391</v>
@@ -672,16 +672,16 @@
         <v>3.75737228701621</v>
       </c>
       <c r="H2" t="n">
-        <v>8.009658703527407</v>
+        <v>408.0096587035274</v>
       </c>
       <c r="I2" t="n">
-        <v>97.45019138541475</v>
+        <v>150.0811596826846</v>
       </c>
       <c r="J2" t="n">
         <v>419.7382696589336</v>
       </c>
       <c r="K2" t="n">
-        <v>279.7604168367271</v>
+        <v>66.13418277953816</v>
       </c>
       <c r="L2" t="n">
         <v>815</v>
@@ -693,31 +693,31 @@
         <v>195.5855355810472</v>
       </c>
       <c r="O2" t="n">
-        <v>815</v>
+        <v>601.8153451151106</v>
       </c>
       <c r="P2" t="n">
         <v>0</v>
       </c>
       <c r="Q2" t="n">
-        <v>371.9706110579117</v>
+        <v>798.7814999999999</v>
       </c>
       <c r="R2" t="n">
-        <v>0</v>
+        <v>250.8785988282945</v>
       </c>
       <c r="S2" t="n">
-        <v>94.84816780232291</v>
+        <v>494.8481678023229</v>
       </c>
       <c r="T2" t="n">
-        <v>586.6755817285639</v>
+        <v>186.6755817285639</v>
       </c>
       <c r="U2" t="n">
         <v>249.2212965486107</v>
       </c>
       <c r="V2" t="n">
-        <v>629.8510241668239</v>
+        <v>229.8510241668239</v>
       </c>
       <c r="W2" t="n">
-        <v>238.3734759809475</v>
+        <v>334.8639088553829</v>
       </c>
       <c r="X2" t="n">
         <v>192.2818334606677</v>
@@ -733,19 +733,19 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>284.6463592929431</v>
+        <v>0</v>
       </c>
       <c r="C3" t="n">
         <v>0</v>
       </c>
       <c r="D3" t="n">
-        <v>0</v>
+        <v>347.9376868977026</v>
       </c>
       <c r="E3" t="n">
-        <v>0</v>
+        <v>342.6720972219126</v>
       </c>
       <c r="F3" t="n">
-        <v>0</v>
+        <v>167.115840263807</v>
       </c>
       <c r="G3" t="n">
         <v>0</v>
@@ -778,7 +778,7 @@
         <v>0</v>
       </c>
       <c r="Q3" t="n">
-        <v>173.0792650904796</v>
+        <v>0</v>
       </c>
       <c r="R3" t="n">
         <v>147.2737972923793</v>
@@ -790,7 +790,7 @@
         <v>5.357765217513816</v>
       </c>
       <c r="U3" t="n">
-        <v>400.2103597601867</v>
+        <v>0.2103597601867477</v>
       </c>
       <c r="V3" t="n">
         <v>14.51066719152016</v>
@@ -903,31 +903,31 @@
         <v>4.363289606868648</v>
       </c>
       <c r="F5" t="n">
-        <v>4.889628708011855</v>
+        <v>404.8896287080119</v>
       </c>
       <c r="G5" t="n">
-        <v>403.7573722870162</v>
+        <v>250.3289648441362</v>
       </c>
       <c r="H5" t="n">
-        <v>8.009658703527407</v>
+        <v>408.0096587035274</v>
       </c>
       <c r="I5" t="n">
-        <v>150.0811596826846</v>
+        <v>0</v>
       </c>
       <c r="J5" t="n">
         <v>798.7814999999999</v>
       </c>
       <c r="K5" t="n">
-        <v>747.707886193033</v>
+        <v>231.6989682850179</v>
       </c>
       <c r="L5" t="n">
         <v>815</v>
       </c>
       <c r="M5" t="n">
-        <v>298.9910820919849</v>
+        <v>815</v>
       </c>
       <c r="N5" t="n">
-        <v>163.5948358836905</v>
+        <v>163.5948358836821</v>
       </c>
       <c r="O5" t="n">
         <v>0</v>
@@ -939,19 +939,19 @@
         <v>371.9706110579117</v>
       </c>
       <c r="R5" t="n">
-        <v>0</v>
+        <v>250.8785988282945</v>
       </c>
       <c r="S5" t="n">
         <v>494.8481678023229</v>
       </c>
       <c r="T5" t="n">
-        <v>534.0446134312941</v>
+        <v>186.6755817285639</v>
       </c>
       <c r="U5" t="n">
         <v>249.2212965486107</v>
       </c>
       <c r="V5" t="n">
-        <v>629.8510241668239</v>
+        <v>229.8510241668239</v>
       </c>
       <c r="W5" t="n">
         <v>238.3734759809475</v>
@@ -973,13 +973,13 @@
         <v>0</v>
       </c>
       <c r="C6" t="n">
-        <v>0</v>
+        <v>109.7879374857201</v>
       </c>
       <c r="D6" t="n">
-        <v>341.9742620710304</v>
+        <v>347.9376868977026</v>
       </c>
       <c r="E6" t="n">
-        <v>342.6720972219126</v>
+        <v>0</v>
       </c>
       <c r="F6" t="n">
         <v>0</v>
@@ -1015,7 +1015,7 @@
         <v>0</v>
       </c>
       <c r="Q6" t="n">
-        <v>173.0792650904796</v>
+        <v>0</v>
       </c>
       <c r="R6" t="n">
         <v>147.2737972923793</v>
@@ -1027,7 +1027,7 @@
         <v>5.357765217513816</v>
       </c>
       <c r="U6" t="n">
-        <v>0.2103597601867477</v>
+        <v>400.2103597601867</v>
       </c>
       <c r="V6" t="n">
         <v>14.51066719152016</v>
@@ -1134,40 +1134,40 @@
         <v>449.4745782429939</v>
       </c>
       <c r="D8" t="n">
-        <v>410.3391557398498</v>
+        <v>10.33915573984979</v>
       </c>
       <c r="E8" t="n">
         <v>4.363289606868648</v>
       </c>
       <c r="F8" t="n">
-        <v>4.889628708011855</v>
+        <v>404.8896287080119</v>
       </c>
       <c r="G8" t="n">
-        <v>250.328964844136</v>
+        <v>351.1264039897461</v>
       </c>
       <c r="H8" t="n">
         <v>408.0096587035274</v>
       </c>
       <c r="I8" t="n">
-        <v>0</v>
+        <v>150.0811596826846</v>
       </c>
       <c r="J8" t="n">
-        <v>798.7814999999999</v>
+        <v>419.7382696589336</v>
       </c>
       <c r="K8" t="n">
-        <v>66.13418277955496</v>
+        <v>66.13418277954936</v>
       </c>
       <c r="L8" t="n">
-        <v>649.5830037161322</v>
+        <v>815</v>
       </c>
       <c r="M8" t="n">
-        <v>298.9910820919849</v>
+        <v>815</v>
       </c>
       <c r="N8" t="n">
         <v>195.5855355810472</v>
       </c>
       <c r="O8" t="n">
-        <v>815</v>
+        <v>512.6173161491834</v>
       </c>
       <c r="P8" t="n">
         <v>0</v>
@@ -1176,7 +1176,7 @@
         <v>371.9706110579117</v>
       </c>
       <c r="R8" t="n">
-        <v>250.8785988282945</v>
+        <v>0</v>
       </c>
       <c r="S8" t="n">
         <v>94.84816780232291</v>
@@ -1213,7 +1213,7 @@
         <v>0</v>
       </c>
       <c r="D9" t="n">
-        <v>0</v>
+        <v>118.0893820455457</v>
       </c>
       <c r="E9" t="n">
         <v>0</v>
@@ -1228,7 +1228,7 @@
         <v>0</v>
       </c>
       <c r="I9" t="n">
-        <v>118.0893820455458</v>
+        <v>0</v>
       </c>
       <c r="J9" t="n">
         <v>0</v>
@@ -1255,7 +1255,7 @@
         <v>0</v>
       </c>
       <c r="R9" t="n">
-        <v>547.2737972923793</v>
+        <v>147.2737972923793</v>
       </c>
       <c r="S9" t="n">
         <v>66.5639999646113</v>
@@ -1270,7 +1270,7 @@
         <v>14.51066719152016</v>
       </c>
       <c r="W9" t="n">
-        <v>32.37314290982852</v>
+        <v>432.3731429098285</v>
       </c>
       <c r="X9" t="n">
         <v>19.86273944538755</v>
@@ -1377,10 +1377,10 @@
         <v>179.3632896068686</v>
       </c>
       <c r="F11" t="n">
-        <v>0</v>
+        <v>179.8896287080119</v>
       </c>
       <c r="G11" t="n">
-        <v>0</v>
+        <v>178.7573722870162</v>
       </c>
       <c r="H11" t="n">
         <v>183.0096587035274</v>
@@ -1422,13 +1422,13 @@
         <v>361.6755817285639</v>
       </c>
       <c r="U11" t="n">
-        <v>424.2212965486107</v>
+        <v>0</v>
       </c>
       <c r="V11" t="n">
-        <v>404.8510241668239</v>
+        <v>333.5218250564237</v>
       </c>
       <c r="W11" t="n">
-        <v>276.4699813169644</v>
+        <v>413.3734759809475</v>
       </c>
       <c r="X11" t="n">
         <v>367.2818334606677</v>
@@ -1523,13 +1523,13 @@
         </is>
       </c>
       <c r="B13" t="n">
-        <v>0</v>
+        <v>62.11380033707866</v>
       </c>
       <c r="C13" t="n">
-        <v>0</v>
+        <v>47.72524664804467</v>
       </c>
       <c r="D13" t="n">
-        <v>0</v>
+        <v>60.53621805555548</v>
       </c>
       <c r="E13" t="n">
         <v>0</v>
@@ -1538,10 +1538,10 @@
         <v>0</v>
       </c>
       <c r="G13" t="n">
-        <v>0</v>
+        <v>20.04387284153003</v>
       </c>
       <c r="H13" t="n">
-        <v>3.77112610161862</v>
+        <v>0</v>
       </c>
       <c r="I13" t="n">
         <v>0</v>
@@ -1568,10 +1568,10 @@
         <v>0</v>
       </c>
       <c r="Q13" t="n">
-        <v>340.7767994885276</v>
+        <v>0</v>
       </c>
       <c r="R13" t="n">
-        <v>0</v>
+        <v>155.5015975466471</v>
       </c>
       <c r="S13" t="n">
         <v>0</v>
@@ -1586,7 +1586,7 @@
         <v>0</v>
       </c>
       <c r="W13" t="n">
-        <v>1.372809838709685</v>
+        <v>0</v>
       </c>
       <c r="X13" t="n">
         <v>0</v>
@@ -1620,7 +1620,7 @@
         <v>124.7573722870162</v>
       </c>
       <c r="H14" t="n">
-        <v>132.4598500889414</v>
+        <v>129.0096587035274</v>
       </c>
       <c r="I14" t="n">
         <v>0</v>
@@ -1665,7 +1665,7 @@
         <v>350.8510241668239</v>
       </c>
       <c r="W14" t="n">
-        <v>359.3734759809475</v>
+        <v>362.8236673663616</v>
       </c>
       <c r="X14" t="n">
         <v>313.2818334606677</v>
@@ -1790,25 +1790,25 @@
         <v>0</v>
       </c>
       <c r="L16" t="n">
-        <v>0</v>
+        <v>144.5476281577792</v>
       </c>
       <c r="M16" t="n">
         <v>0</v>
       </c>
       <c r="N16" t="n">
-        <v>0</v>
+        <v>280.2477035451817</v>
       </c>
       <c r="O16" t="n">
-        <v>0</v>
+        <v>361.445564079015</v>
       </c>
       <c r="P16" t="n">
-        <v>408.4478973282775</v>
+        <v>0</v>
       </c>
       <c r="Q16" t="n">
         <v>0</v>
       </c>
       <c r="R16" t="n">
-        <v>377.7929984536983</v>
+        <v>0</v>
       </c>
       <c r="S16" t="n">
         <v>0</v>
@@ -1887,10 +1887,10 @@
         <v>0</v>
       </c>
       <c r="R17" t="n">
-        <v>0</v>
+        <v>3.450191385414405</v>
       </c>
       <c r="S17" t="n">
-        <v>219.2983591877372</v>
+        <v>215.8481678023229</v>
       </c>
       <c r="T17" t="n">
         <v>307.6755817285639</v>
@@ -2036,19 +2036,19 @@
         <v>0</v>
       </c>
       <c r="O19" t="n">
-        <v>0</v>
+        <v>361.445564079015</v>
       </c>
       <c r="P19" t="n">
-        <v>339.4016293563778</v>
+        <v>0</v>
       </c>
       <c r="Q19" t="n">
-        <v>446.839266425598</v>
+        <v>0</v>
       </c>
       <c r="R19" t="n">
-        <v>0</v>
+        <v>341.4218520001054</v>
       </c>
       <c r="S19" t="n">
-        <v>0</v>
+        <v>83.37347970285543</v>
       </c>
       <c r="T19" t="n">
         <v>0</v>
@@ -2094,10 +2094,10 @@
         <v>124.7573722870162</v>
       </c>
       <c r="H20" t="n">
-        <v>129.0096587035274</v>
+        <v>132.4598500889414</v>
       </c>
       <c r="I20" t="n">
-        <v>3.450191385413969</v>
+        <v>0</v>
       </c>
       <c r="J20" t="n">
         <v>0</v>
@@ -2234,13 +2234,13 @@
         </is>
       </c>
       <c r="B22" t="n">
-        <v>0</v>
+        <v>8.113800337078658</v>
       </c>
       <c r="C22" t="n">
         <v>0</v>
       </c>
       <c r="D22" t="n">
-        <v>0</v>
+        <v>6.53621805555548</v>
       </c>
       <c r="E22" t="n">
         <v>0</v>
@@ -2273,19 +2273,19 @@
         <v>0</v>
       </c>
       <c r="O22" t="n">
-        <v>361.445564079015</v>
+        <v>0</v>
       </c>
       <c r="P22" t="n">
-        <v>0</v>
+        <v>408.4478973282775</v>
       </c>
       <c r="Q22" t="n">
         <v>0</v>
       </c>
       <c r="R22" t="n">
-        <v>424.7953317029608</v>
+        <v>279.7695003582087</v>
       </c>
       <c r="S22" t="n">
-        <v>0</v>
+        <v>83.37347970285543</v>
       </c>
       <c r="T22" t="n">
         <v>0</v>
@@ -2328,13 +2328,13 @@
         <v>125.8896287080119</v>
       </c>
       <c r="G23" t="n">
-        <v>124.7573722870162</v>
+        <v>128.2075636724302</v>
       </c>
       <c r="H23" t="n">
         <v>129.0096587035274</v>
       </c>
       <c r="I23" t="n">
-        <v>3.450191385413969</v>
+        <v>0</v>
       </c>
       <c r="J23" t="n">
         <v>0</v>
@@ -2477,7 +2477,7 @@
         <v>0</v>
       </c>
       <c r="D25" t="n">
-        <v>0</v>
+        <v>6.53621805555548</v>
       </c>
       <c r="E25" t="n">
         <v>0</v>
@@ -2501,10 +2501,10 @@
         <v>0</v>
       </c>
       <c r="L25" t="n">
-        <v>0</v>
+        <v>90.47093834271922</v>
       </c>
       <c r="M25" t="n">
-        <v>0</v>
+        <v>241.6316114025499</v>
       </c>
       <c r="N25" t="n">
         <v>0</v>
@@ -2516,7 +2516,7 @@
         <v>0</v>
       </c>
       <c r="Q25" t="n">
-        <v>338.6387678008247</v>
+        <v>0</v>
       </c>
       <c r="R25" t="n">
         <v>447.6021279811511</v>
@@ -2559,13 +2559,13 @@
         <v>185.3391557398498</v>
       </c>
       <c r="E26" t="n">
-        <v>0</v>
+        <v>179.3632896068686</v>
       </c>
       <c r="F26" t="n">
-        <v>44.09437970762736</v>
+        <v>0</v>
       </c>
       <c r="G26" t="n">
-        <v>0</v>
+        <v>178.7573722870162</v>
       </c>
       <c r="H26" t="n">
         <v>183.0096587035274</v>
@@ -2607,16 +2607,16 @@
         <v>361.6755817285639</v>
       </c>
       <c r="U26" t="n">
-        <v>0</v>
+        <v>424.2212965486107</v>
       </c>
       <c r="V26" t="n">
-        <v>404.8510241668239</v>
+        <v>0</v>
       </c>
       <c r="W26" t="n">
         <v>413.3734759809475</v>
       </c>
       <c r="X26" t="n">
-        <v>367.2818334606677</v>
+        <v>33.88527889262345</v>
       </c>
       <c r="Y26" t="n">
         <v>286.3174326828064</v>
@@ -2708,7 +2708,7 @@
         </is>
       </c>
       <c r="B28" t="n">
-        <v>0</v>
+        <v>62.11380033707866</v>
       </c>
       <c r="C28" t="n">
         <v>0</v>
@@ -2720,7 +2720,7 @@
         <v>0</v>
       </c>
       <c r="F28" t="n">
-        <v>0</v>
+        <v>46.67635559750978</v>
       </c>
       <c r="G28" t="n">
         <v>0</v>
@@ -2756,7 +2756,7 @@
         <v>0</v>
       </c>
       <c r="R28" t="n">
-        <v>340.7767994885276</v>
+        <v>233.3594533926489</v>
       </c>
       <c r="S28" t="n">
         <v>0</v>
@@ -2771,7 +2771,7 @@
         <v>0</v>
       </c>
       <c r="W28" t="n">
-        <v>1.372809838709685</v>
+        <v>0</v>
       </c>
       <c r="X28" t="n">
         <v>0</v>
@@ -2796,16 +2796,16 @@
         <v>159.3391557398498</v>
       </c>
       <c r="E29" t="n">
-        <v>0</v>
+        <v>153.3632896068686</v>
       </c>
       <c r="F29" t="n">
-        <v>0</v>
+        <v>153.8896287080119</v>
       </c>
       <c r="G29" t="n">
-        <v>0</v>
+        <v>152.7573722870162</v>
       </c>
       <c r="H29" t="n">
-        <v>88.76134069083864</v>
+        <v>0</v>
       </c>
       <c r="I29" t="n">
         <v>0</v>
@@ -2844,7 +2844,7 @@
         <v>335.6755817285639</v>
       </c>
       <c r="U29" t="n">
-        <v>398.2212965486107</v>
+        <v>26.9723466375526</v>
       </c>
       <c r="V29" t="n">
         <v>378.8510241668239</v>
@@ -2984,16 +2984,16 @@
         <v>0</v>
       </c>
       <c r="O31" t="n">
-        <v>389.445564079015</v>
+        <v>0</v>
       </c>
       <c r="P31" t="n">
-        <v>139.1349830766932</v>
+        <v>52.97841917455702</v>
       </c>
       <c r="Q31" t="n">
         <v>0</v>
       </c>
       <c r="R31" t="n">
-        <v>0</v>
+        <v>475.6021279811511</v>
       </c>
       <c r="S31" t="n">
         <v>0</v>
@@ -3054,7 +3054,7 @@
         <v>0</v>
       </c>
       <c r="L32" t="n">
-        <v>47.83862152370594</v>
+        <v>0</v>
       </c>
       <c r="M32" t="n">
         <v>0</v>
@@ -3063,7 +3063,7 @@
         <v>0</v>
       </c>
       <c r="O32" t="n">
-        <v>0</v>
+        <v>47.83862152370919</v>
       </c>
       <c r="P32" t="n">
         <v>0</v>
@@ -3075,7 +3075,7 @@
         <v>0</v>
       </c>
       <c r="S32" t="n">
-        <v>196.5895591877376</v>
+        <v>206.8481678023229</v>
       </c>
       <c r="T32" t="n">
         <v>298.6755817285639</v>
@@ -3093,7 +3093,7 @@
         <v>304.2818334606677</v>
       </c>
       <c r="Y32" t="n">
-        <v>223.3174326828064</v>
+        <v>213.0588240682208</v>
       </c>
     </row>
     <row r="33">
@@ -3212,13 +3212,13 @@
         <v>0</v>
       </c>
       <c r="L34" t="n">
-        <v>0</v>
+        <v>135.5476281577792</v>
       </c>
       <c r="M34" t="n">
         <v>0</v>
       </c>
       <c r="N34" t="n">
-        <v>0</v>
+        <v>6.516446031824193</v>
       </c>
       <c r="O34" t="n">
         <v>352.445564079015</v>
@@ -3227,7 +3227,7 @@
         <v>399.4478973282775</v>
       </c>
       <c r="Q34" t="n">
-        <v>142.0640741896034</v>
+        <v>0</v>
       </c>
       <c r="R34" t="n">
         <v>0</v>
@@ -3279,7 +3279,7 @@
         <v>115.7573722870162</v>
       </c>
       <c r="H35" t="n">
-        <v>109.7510500892273</v>
+        <v>120.0096587035274</v>
       </c>
       <c r="I35" t="n">
         <v>0</v>
@@ -3297,7 +3297,7 @@
         <v>0</v>
       </c>
       <c r="N35" t="n">
-        <v>47.83862153326641</v>
+        <v>47.83862152369411</v>
       </c>
       <c r="O35" t="n">
         <v>0</v>
@@ -3318,7 +3318,7 @@
         <v>298.6755817285639</v>
       </c>
       <c r="U35" t="n">
-        <v>361.2212965486107</v>
+        <v>350.9626879340248</v>
       </c>
       <c r="V35" t="n">
         <v>341.8510241668239</v>
@@ -3452,7 +3452,7 @@
         <v>135.5476281577792</v>
       </c>
       <c r="M37" t="n">
-        <v>232.6316114025499</v>
+        <v>0</v>
       </c>
       <c r="N37" t="n">
         <v>0</v>
@@ -3464,7 +3464,7 @@
         <v>0</v>
       </c>
       <c r="Q37" t="n">
-        <v>12.80268835256014</v>
+        <v>245.4342997551101</v>
       </c>
       <c r="R37" t="n">
         <v>438.6021279811511</v>
@@ -3525,10 +3525,10 @@
         <v>0</v>
       </c>
       <c r="K38" t="n">
-        <v>20.16895504768641</v>
+        <v>47.83862152375633</v>
       </c>
       <c r="L38" t="n">
-        <v>27.66966648845096</v>
+        <v>0</v>
       </c>
       <c r="M38" t="n">
         <v>0</v>
@@ -3567,7 +3567,7 @@
         <v>304.2818334606677</v>
       </c>
       <c r="Y38" t="n">
-        <v>213.0588240685926</v>
+        <v>213.0588240682208</v>
       </c>
     </row>
     <row r="39">
@@ -3686,7 +3686,7 @@
         <v>0</v>
       </c>
       <c r="L40" t="n">
-        <v>0</v>
+        <v>135.5476281577792</v>
       </c>
       <c r="M40" t="n">
         <v>0</v>
@@ -3695,19 +3695,19 @@
         <v>0</v>
       </c>
       <c r="O40" t="n">
-        <v>56.67037184302036</v>
+        <v>0</v>
       </c>
       <c r="P40" t="n">
-        <v>399.4478973282775</v>
+        <v>0</v>
       </c>
       <c r="Q40" t="n">
-        <v>437.839266425598</v>
+        <v>245.4342997551101</v>
       </c>
       <c r="R40" t="n">
-        <v>0</v>
+        <v>438.6021279811511</v>
       </c>
       <c r="S40" t="n">
-        <v>0</v>
+        <v>74.37347970285543</v>
       </c>
       <c r="T40" t="n">
         <v>0</v>
@@ -3735,19 +3735,19 @@
         </is>
       </c>
       <c r="B41" t="n">
-        <v>286.9993129555745</v>
+        <v>0</v>
       </c>
       <c r="C41" t="n">
         <v>0</v>
       </c>
       <c r="D41" t="n">
-        <v>0</v>
+        <v>215.3391557398498</v>
       </c>
       <c r="E41" t="n">
         <v>0</v>
       </c>
       <c r="F41" t="n">
-        <v>0</v>
+        <v>198.6288078182531</v>
       </c>
       <c r="G41" t="n">
         <v>0</v>
@@ -3786,7 +3786,7 @@
         <v>55.87859882829446</v>
       </c>
       <c r="S41" t="n">
-        <v>29.53498494418355</v>
+        <v>299.8481678023229</v>
       </c>
       <c r="T41" t="n">
         <v>391.6755817285639</v>
@@ -3801,7 +3801,7 @@
         <v>443.3734759809475</v>
       </c>
       <c r="X41" t="n">
-        <v>397.2818334606677</v>
+        <v>0</v>
       </c>
       <c r="Y41" t="n">
         <v>316.3174326828064</v>
@@ -3865,7 +3865,7 @@
         <v>0</v>
       </c>
       <c r="S42" t="n">
-        <v>217.5960513602861</v>
+        <v>0</v>
       </c>
       <c r="T42" t="n">
         <v>210.3577652175138</v>
@@ -3877,7 +3877,7 @@
         <v>219.5106671915202</v>
       </c>
       <c r="W42" t="n">
-        <v>0</v>
+        <v>236.711783115919</v>
       </c>
       <c r="X42" t="n">
         <v>224.8627394453875</v>
@@ -3911,7 +3911,7 @@
         <v>0</v>
       </c>
       <c r="H43" t="n">
-        <v>33.77112610161862</v>
+        <v>0</v>
       </c>
       <c r="I43" t="n">
         <v>0</v>
@@ -3972,28 +3972,28 @@
         </is>
       </c>
       <c r="B44" t="n">
-        <v>0</v>
+        <v>366.9993129555745</v>
       </c>
       <c r="C44" t="n">
-        <v>0</v>
+        <v>227.8442897030557</v>
       </c>
       <c r="D44" t="n">
-        <v>0</v>
+        <v>295.3391557398498</v>
       </c>
       <c r="E44" t="n">
         <v>289.3632896068686</v>
       </c>
       <c r="F44" t="n">
-        <v>289.8896287080119</v>
+        <v>0</v>
       </c>
       <c r="G44" t="n">
         <v>0</v>
       </c>
       <c r="H44" t="n">
-        <v>0</v>
+        <v>293.0096587035274</v>
       </c>
       <c r="I44" t="n">
-        <v>0</v>
+        <v>35.08115968268461</v>
       </c>
       <c r="J44" t="n">
         <v>0</v>
@@ -4029,7 +4029,7 @@
         <v>0</v>
       </c>
       <c r="U44" t="n">
-        <v>532.0665153938742</v>
+        <v>0</v>
       </c>
       <c r="V44" t="n">
         <v>514.8510241668239</v>
@@ -4041,7 +4041,7 @@
         <v>477.2818334606677</v>
       </c>
       <c r="Y44" t="n">
-        <v>396.3174326828064</v>
+        <v>0</v>
       </c>
     </row>
     <row r="45">
@@ -4051,19 +4051,19 @@
         </is>
       </c>
       <c r="B45" t="n">
-        <v>0</v>
+        <v>269.5565566463266</v>
       </c>
       <c r="C45" t="n">
-        <v>0</v>
+        <v>246.0999124455193</v>
       </c>
       <c r="D45" t="n">
-        <v>0</v>
+        <v>232.9376868977026</v>
       </c>
       <c r="E45" t="n">
-        <v>0</v>
+        <v>227.6720972219126</v>
       </c>
       <c r="F45" t="n">
-        <v>0</v>
+        <v>224.6362423378769</v>
       </c>
       <c r="G45" t="n">
         <v>0</v>
@@ -4072,7 +4072,7 @@
         <v>0</v>
       </c>
       <c r="I45" t="n">
-        <v>0</v>
+        <v>102.1263858913485</v>
       </c>
       <c r="J45" t="n">
         <v>0</v>
@@ -4096,25 +4096,25 @@
         <v>0</v>
       </c>
       <c r="Q45" t="n">
-        <v>58.07926509047959</v>
+        <v>0</v>
       </c>
       <c r="R45" t="n">
-        <v>432.2737972923793</v>
+        <v>0</v>
       </c>
       <c r="S45" t="n">
-        <v>0</v>
+        <v>154.8364092410399</v>
       </c>
       <c r="T45" t="n">
-        <v>290.3577652175138</v>
+        <v>0</v>
       </c>
       <c r="U45" t="n">
-        <v>285.2103597601867</v>
+        <v>0</v>
       </c>
       <c r="V45" t="n">
-        <v>299.5106671915202</v>
+        <v>0</v>
       </c>
       <c r="W45" t="n">
-        <v>136.6661172122473</v>
+        <v>0</v>
       </c>
       <c r="X45" t="n">
         <v>304.8627394453875</v>
@@ -4184,7 +4184,7 @@
         <v>0</v>
       </c>
       <c r="T46" t="n">
-        <v>0</v>
+        <v>78.1444032459268</v>
       </c>
       <c r="U46" t="n">
         <v>0</v>
@@ -4297,25 +4297,25 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>245.2847218926087</v>
+        <v>702.4877201726792</v>
       </c>
       <c r="C2" t="n">
-        <v>195.3104004350391</v>
+        <v>652.5133987151096</v>
       </c>
       <c r="D2" t="n">
-        <v>184.8668087786251</v>
+        <v>642.0698070586957</v>
       </c>
       <c r="E2" t="n">
-        <v>180.4594455393639</v>
+        <v>637.6624438194344</v>
       </c>
       <c r="F2" t="n">
-        <v>175.5204266423822</v>
+        <v>632.7234249224528</v>
       </c>
       <c r="G2" t="n">
-        <v>171.7251010999416</v>
+        <v>628.9280993800121</v>
       </c>
       <c r="H2" t="n">
-        <v>163.6345367529442</v>
+        <v>216.7971309926107</v>
       </c>
       <c r="I2" t="n">
         <v>65.2</v>
@@ -4324,49 +4324,49 @@
         <v>448.0719498394611</v>
       </c>
       <c r="K2" t="n">
-        <v>940.6648775060045</v>
+        <v>1156.448952311256</v>
       </c>
       <c r="L2" t="n">
-        <v>924.2825542736812</v>
+        <v>1140.066629078932</v>
       </c>
       <c r="M2" t="n">
-        <v>1429.121360241373</v>
+        <v>1644.905435046624</v>
       </c>
       <c r="N2" t="n">
-        <v>2038.41021318981</v>
+        <v>2254.194287995062</v>
       </c>
       <c r="O2" t="n">
-        <v>2022.027889957487</v>
+        <v>2453.15</v>
       </c>
       <c r="P2" t="n">
-        <v>2828.877889957487</v>
+        <v>3260</v>
       </c>
       <c r="Q2" t="n">
         <v>3260</v>
       </c>
       <c r="R2" t="n">
-        <v>3260</v>
+        <v>3006.587273910814</v>
       </c>
       <c r="S2" t="n">
-        <v>3164.193769896644</v>
+        <v>2506.740639767053</v>
       </c>
       <c r="T2" t="n">
-        <v>2571.592172191024</v>
+        <v>2318.179446101837</v>
       </c>
       <c r="U2" t="n">
-        <v>2319.853488808589</v>
+        <v>2066.440762719402</v>
       </c>
       <c r="V2" t="n">
-        <v>1683.640333084524</v>
+        <v>1834.268011035741</v>
       </c>
       <c r="W2" t="n">
-        <v>1442.85904421488</v>
+        <v>1496.021638454547</v>
       </c>
       <c r="X2" t="n">
-        <v>1248.634970012185</v>
+        <v>1301.797564251852</v>
       </c>
       <c r="Y2" t="n">
-        <v>732.1527147770274</v>
+        <v>785.3153090166938</v>
       </c>
     </row>
     <row r="3">
@@ -4376,76 +4376,76 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>65.2</v>
+        <v>2970.957099210679</v>
       </c>
       <c r="C3" t="n">
-        <v>65.2</v>
+        <v>2970.957099210679</v>
       </c>
       <c r="D3" t="n">
-        <v>65.2</v>
+        <v>2619.504890223101</v>
       </c>
       <c r="E3" t="n">
-        <v>65.2</v>
+        <v>2273.371458685815</v>
       </c>
       <c r="F3" t="n">
-        <v>65.2</v>
+        <v>2104.567579631464</v>
       </c>
       <c r="G3" t="n">
-        <v>65.2</v>
+        <v>2104.567579631464</v>
       </c>
       <c r="H3" t="n">
-        <v>65.2</v>
+        <v>2104.567579631464</v>
       </c>
       <c r="I3" t="n">
-        <v>65.2</v>
+        <v>2104.567579631464</v>
       </c>
       <c r="J3" t="n">
-        <v>189.156520175299</v>
+        <v>2228.524099806763</v>
       </c>
       <c r="K3" t="n">
-        <v>378.3493362696823</v>
+        <v>2417.716915901147</v>
       </c>
       <c r="L3" t="n">
-        <v>649.6997978648824</v>
+        <v>2689.067377496347</v>
       </c>
       <c r="M3" t="n">
-        <v>735.7803396077417</v>
+        <v>2775.147919239206</v>
       </c>
       <c r="N3" t="n">
-        <v>869.06062421531</v>
+        <v>2908.428203846775</v>
       </c>
       <c r="O3" t="n">
-        <v>1108.103075899029</v>
+        <v>3147.470655530493</v>
       </c>
       <c r="P3" t="n">
-        <v>1220.632420368536</v>
+        <v>3260</v>
       </c>
       <c r="Q3" t="n">
-        <v>1045.804879873102</v>
+        <v>3260</v>
       </c>
       <c r="R3" t="n">
-        <v>897.0434684666577</v>
+        <v>3111.238588593556</v>
       </c>
       <c r="S3" t="n">
-        <v>829.8071048660403</v>
+        <v>3044.002224992939</v>
       </c>
       <c r="T3" t="n">
-        <v>824.3952208079455</v>
+        <v>3038.590340934844</v>
       </c>
       <c r="U3" t="n">
-        <v>420.1423321612922</v>
+        <v>3038.377856328595</v>
       </c>
       <c r="V3" t="n">
-        <v>405.4850925738981</v>
+        <v>3023.720616741201</v>
       </c>
       <c r="W3" t="n">
-        <v>372.784948220536</v>
+        <v>2991.020472387838</v>
       </c>
       <c r="X3" t="n">
-        <v>352.7215750433768</v>
+        <v>2970.957099210679</v>
       </c>
       <c r="Y3" t="n">
-        <v>352.7215750433768</v>
+        <v>2970.957099210679</v>
       </c>
     </row>
     <row r="4">
@@ -4455,25 +4455,25 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>318.31316170179</v>
+        <v>692.8526065247581</v>
       </c>
       <c r="C4" t="n">
-        <v>318.31316170179</v>
+        <v>692.8526065247581</v>
       </c>
       <c r="D4" t="n">
-        <v>318.31316170179</v>
+        <v>692.8526065247581</v>
       </c>
       <c r="E4" t="n">
-        <v>436.1420659132031</v>
+        <v>810.6815107361712</v>
       </c>
       <c r="F4" t="n">
-        <v>560.5030385051385</v>
+        <v>935.0424833281066</v>
       </c>
       <c r="G4" t="n">
-        <v>713.9096043920238</v>
+        <v>935.0424833281066</v>
       </c>
       <c r="H4" t="n">
-        <v>883.4261895514213</v>
+        <v>1104.559068487504</v>
       </c>
       <c r="I4" t="n">
         <v>1104.559068487504</v>
@@ -4506,25 +4506,25 @@
         <v>65.2</v>
       </c>
       <c r="S4" t="n">
-        <v>102.4502550941731</v>
+        <v>65.2</v>
       </c>
       <c r="T4" t="n">
-        <v>146.4222434421126</v>
+        <v>253.2756791588048</v>
       </c>
       <c r="U4" t="n">
-        <v>146.4222434421126</v>
+        <v>409.5523875860484</v>
       </c>
       <c r="V4" t="n">
-        <v>146.4222434421126</v>
+        <v>409.5523875860484</v>
       </c>
       <c r="W4" t="n">
-        <v>318.31316170179</v>
+        <v>581.4433058457258</v>
       </c>
       <c r="X4" t="n">
-        <v>318.31316170179</v>
+        <v>581.4433058457258</v>
       </c>
       <c r="Y4" t="n">
-        <v>318.31316170179</v>
+        <v>692.8526065247581</v>
       </c>
     </row>
     <row r="5">
@@ -4534,25 +4534,25 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>702.4877201726792</v>
+        <v>1203.993207924634</v>
       </c>
       <c r="C5" t="n">
-        <v>652.5133987151096</v>
+        <v>1154.018886467064</v>
       </c>
       <c r="D5" t="n">
-        <v>642.0698070586957</v>
+        <v>1143.575294810651</v>
       </c>
       <c r="E5" t="n">
-        <v>637.6624438194344</v>
+        <v>1139.167931571389</v>
       </c>
       <c r="F5" t="n">
-        <v>632.7234249224528</v>
+        <v>730.1885086340036</v>
       </c>
       <c r="G5" t="n">
-        <v>224.8876953396081</v>
+        <v>477.3309683874014</v>
       </c>
       <c r="H5" t="n">
-        <v>216.7971309926107</v>
+        <v>65.2</v>
       </c>
       <c r="I5" t="n">
         <v>65.2</v>
@@ -4561,13 +4561,13 @@
         <v>65.2</v>
       </c>
       <c r="K5" t="n">
-        <v>116.7895088959262</v>
+        <v>638.0106380959415</v>
       </c>
       <c r="L5" t="n">
-        <v>100.4071856636029</v>
+        <v>621.6283148636181</v>
       </c>
       <c r="M5" t="n">
-        <v>605.2459916312948</v>
+        <v>605.2459916312947</v>
       </c>
       <c r="N5" t="n">
         <v>1215.177889957487</v>
@@ -4582,28 +4582,28 @@
         <v>3260</v>
       </c>
       <c r="R5" t="n">
-        <v>3260</v>
+        <v>3006.587273910814</v>
       </c>
       <c r="S5" t="n">
-        <v>2760.153365856239</v>
+        <v>2506.740639767053</v>
       </c>
       <c r="T5" t="n">
-        <v>2220.714362390286</v>
+        <v>2318.179446101837</v>
       </c>
       <c r="U5" t="n">
-        <v>1968.975679007851</v>
+        <v>2066.440762719402</v>
       </c>
       <c r="V5" t="n">
-        <v>1332.762523283786</v>
+        <v>1834.268011035741</v>
       </c>
       <c r="W5" t="n">
-        <v>1091.981234414142</v>
+        <v>1593.486722166097</v>
       </c>
       <c r="X5" t="n">
-        <v>897.7571602114477</v>
+        <v>1399.262647963403</v>
       </c>
       <c r="Y5" t="n">
-        <v>785.3153090166938</v>
+        <v>1286.820796768649</v>
       </c>
     </row>
     <row r="6">
@@ -4613,13 +4613,13 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>756.7619790837808</v>
+        <v>527.5491155388108</v>
       </c>
       <c r="C6" t="n">
-        <v>756.7619790837808</v>
+        <v>416.6522089875784</v>
       </c>
       <c r="D6" t="n">
-        <v>411.3334315372855</v>
+        <v>65.2</v>
       </c>
       <c r="E6" t="n">
         <v>65.2</v>
@@ -4658,31 +4658,31 @@
         <v>1220.632420368536</v>
       </c>
       <c r="Q6" t="n">
-        <v>1045.804879873102</v>
+        <v>1220.632420368536</v>
       </c>
       <c r="R6" t="n">
-        <v>897.0434684666577</v>
+        <v>1071.871008962092</v>
       </c>
       <c r="S6" t="n">
-        <v>829.8071048660403</v>
+        <v>1004.634645361474</v>
       </c>
       <c r="T6" t="n">
-        <v>824.3952208079455</v>
+        <v>999.2227613033796</v>
       </c>
       <c r="U6" t="n">
-        <v>824.1827362016962</v>
+        <v>594.9698726567262</v>
       </c>
       <c r="V6" t="n">
-        <v>809.5254966143021</v>
+        <v>580.3126330693322</v>
       </c>
       <c r="W6" t="n">
-        <v>776.82535226094</v>
+        <v>547.61248871597</v>
       </c>
       <c r="X6" t="n">
-        <v>756.7619790837808</v>
+        <v>527.5491155388108</v>
       </c>
       <c r="Y6" t="n">
-        <v>756.7619790837808</v>
+        <v>527.5491155388108</v>
       </c>
     </row>
     <row r="7">
@@ -4692,19 +4692,19 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>566.077758229241</v>
+        <v>847.3599956093144</v>
       </c>
       <c r="C7" t="n">
-        <v>566.077758229241</v>
+        <v>847.3599956093144</v>
       </c>
       <c r="D7" t="n">
-        <v>679.3969023542411</v>
+        <v>847.3599956093144</v>
       </c>
       <c r="E7" t="n">
-        <v>797.2258065656541</v>
+        <v>965.1888998207274</v>
       </c>
       <c r="F7" t="n">
-        <v>921.5867791575896</v>
+        <v>965.1888998207274</v>
       </c>
       <c r="G7" t="n">
         <v>1074.993345044475</v>
@@ -4746,22 +4746,22 @@
         <v>102.4502550941731</v>
       </c>
       <c r="T7" t="n">
-        <v>290.525934252978</v>
+        <v>102.4502550941731</v>
       </c>
       <c r="U7" t="n">
-        <v>537.0771268912647</v>
+        <v>102.4502550941731</v>
       </c>
       <c r="V7" t="n">
-        <v>566.077758229241</v>
+        <v>301.271647980119</v>
       </c>
       <c r="W7" t="n">
-        <v>566.077758229241</v>
+        <v>473.1625662397964</v>
       </c>
       <c r="X7" t="n">
-        <v>566.077758229241</v>
+        <v>624.1933572639899</v>
       </c>
       <c r="Y7" t="n">
-        <v>566.077758229241</v>
+        <v>735.6026579430222</v>
       </c>
     </row>
     <row r="8">
@@ -4771,43 +4771,43 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>1608.033611965038</v>
+        <v>1861.446338054225</v>
       </c>
       <c r="C8" t="n">
-        <v>1154.018886467064</v>
+        <v>1407.431612556251</v>
       </c>
       <c r="D8" t="n">
-        <v>739.5348907702464</v>
+        <v>1396.988020899837</v>
       </c>
       <c r="E8" t="n">
-        <v>735.1275275309852</v>
+        <v>1392.580657660576</v>
       </c>
       <c r="F8" t="n">
-        <v>730.1885086340035</v>
+        <v>983.60123472319</v>
       </c>
       <c r="G8" t="n">
-        <v>477.3309683874014</v>
+        <v>628.9280993800121</v>
       </c>
       <c r="H8" t="n">
-        <v>65.2</v>
+        <v>216.7971309926107</v>
       </c>
       <c r="I8" t="n">
         <v>65.2</v>
       </c>
       <c r="J8" t="n">
-        <v>65.2</v>
+        <v>448.0719498394611</v>
       </c>
       <c r="K8" t="n">
-        <v>773.5770024717946</v>
+        <v>1156.448952311256</v>
       </c>
       <c r="L8" t="n">
-        <v>924.2825542736812</v>
+        <v>1140.066629078932</v>
       </c>
       <c r="M8" t="n">
-        <v>1429.121360241373</v>
+        <v>1123.684305846609</v>
       </c>
       <c r="N8" t="n">
-        <v>2038.41021318981</v>
+        <v>1732.973158795046</v>
       </c>
       <c r="O8" t="n">
         <v>2022.027889957487</v>
@@ -4819,28 +4819,28 @@
         <v>3260</v>
       </c>
       <c r="R8" t="n">
-        <v>3006.587273910814</v>
+        <v>3260</v>
       </c>
       <c r="S8" t="n">
-        <v>2910.781043807457</v>
+        <v>3164.193769896644</v>
       </c>
       <c r="T8" t="n">
-        <v>2722.219850142241</v>
+        <v>2975.632576231427</v>
       </c>
       <c r="U8" t="n">
-        <v>2470.481166759806</v>
+        <v>2723.893892848992</v>
       </c>
       <c r="V8" t="n">
-        <v>2238.308415076146</v>
+        <v>2491.721141165332</v>
       </c>
       <c r="W8" t="n">
-        <v>1997.527126206502</v>
+        <v>2250.939852295688</v>
       </c>
       <c r="X8" t="n">
-        <v>1803.303052003807</v>
+        <v>2056.715778092993</v>
       </c>
       <c r="Y8" t="n">
-        <v>1690.861200809053</v>
+        <v>1944.273926898239</v>
       </c>
     </row>
     <row r="9">
@@ -4850,25 +4850,25 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>527.5491155388108</v>
+        <v>527.5491155388107</v>
       </c>
       <c r="C9" t="n">
-        <v>527.5491155388108</v>
+        <v>527.5491155388107</v>
       </c>
       <c r="D9" t="n">
-        <v>527.5491155388108</v>
+        <v>408.2669114524009</v>
       </c>
       <c r="E9" t="n">
-        <v>527.5491155388108</v>
+        <v>408.2669114524009</v>
       </c>
       <c r="F9" t="n">
-        <v>184.4822040864099</v>
+        <v>65.2</v>
       </c>
       <c r="G9" t="n">
-        <v>184.4822040864099</v>
+        <v>65.2</v>
       </c>
       <c r="H9" t="n">
-        <v>184.4822040864099</v>
+        <v>65.2</v>
       </c>
       <c r="I9" t="n">
         <v>65.2</v>
@@ -4898,28 +4898,28 @@
         <v>1220.632420368536</v>
       </c>
       <c r="R9" t="n">
-        <v>667.8306049216877</v>
+        <v>1071.871008962092</v>
       </c>
       <c r="S9" t="n">
-        <v>600.5942413210703</v>
+        <v>1004.634645361474</v>
       </c>
       <c r="T9" t="n">
-        <v>595.1823572629755</v>
+        <v>999.2227613033796</v>
       </c>
       <c r="U9" t="n">
-        <v>594.9698726567262</v>
+        <v>999.0102766971303</v>
       </c>
       <c r="V9" t="n">
-        <v>580.3126330693322</v>
+        <v>984.3530371097362</v>
       </c>
       <c r="W9" t="n">
-        <v>547.61248871597</v>
+        <v>547.6124887159699</v>
       </c>
       <c r="X9" t="n">
-        <v>527.5491155388108</v>
+        <v>527.5491155388107</v>
       </c>
       <c r="Y9" t="n">
-        <v>527.5491155388108</v>
+        <v>527.5491155388107</v>
       </c>
     </row>
     <row r="10">
@@ -4929,28 +4929,28 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>550.4401863476735</v>
+        <v>1021.569973966908</v>
       </c>
       <c r="C10" t="n">
-        <v>676.4421921661093</v>
+        <v>1147.571979785344</v>
       </c>
       <c r="D10" t="n">
-        <v>789.7613362911094</v>
+        <v>1214.923502424373</v>
       </c>
       <c r="E10" t="n">
-        <v>907.5902405025224</v>
+        <v>1214.923502424373</v>
       </c>
       <c r="F10" t="n">
-        <v>1031.951213094458</v>
+        <v>1214.923502424373</v>
       </c>
       <c r="G10" t="n">
-        <v>1185.357778981343</v>
+        <v>1214.923502424373</v>
       </c>
       <c r="H10" t="n">
-        <v>1354.874364140741</v>
+        <v>1214.923502424373</v>
       </c>
       <c r="I10" t="n">
-        <v>1576.007243076824</v>
+        <v>1214.923502424373</v>
       </c>
       <c r="J10" t="n">
         <v>1576.007243076824</v>
@@ -4986,19 +4986,19 @@
         <v>253.2756791588048</v>
       </c>
       <c r="U10" t="n">
-        <v>327.2735480023491</v>
+        <v>499.8268717970915</v>
       </c>
       <c r="V10" t="n">
-        <v>327.2735480023491</v>
+        <v>698.6482646830375</v>
       </c>
       <c r="W10" t="n">
-        <v>327.2735480023491</v>
+        <v>870.5391829427149</v>
       </c>
       <c r="X10" t="n">
-        <v>327.2735480023491</v>
+        <v>1021.569973966908</v>
       </c>
       <c r="Y10" t="n">
-        <v>438.6828486813814</v>
+        <v>1021.569973966908</v>
       </c>
     </row>
     <row r="11">
@@ -5008,19 +5008,19 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>845.1865477709493</v>
+        <v>1207.456245745725</v>
       </c>
       <c r="C11" t="n">
-        <v>618.4445495457029</v>
+        <v>980.7142475204787</v>
       </c>
       <c r="D11" t="n">
-        <v>431.2332811216122</v>
+        <v>793.502979096388</v>
       </c>
       <c r="E11" t="n">
-        <v>250.0582411146742</v>
+        <v>612.32793908945</v>
       </c>
       <c r="F11" t="n">
-        <v>250.0582411146742</v>
+        <v>430.6212434247915</v>
       </c>
       <c r="G11" t="n">
         <v>250.0582411146742</v>
@@ -5035,16 +5035,16 @@
         <v>456.5091130376557</v>
       </c>
       <c r="K11" t="n">
-        <v>1166.215479385524</v>
+        <v>456.5091130376557</v>
       </c>
       <c r="L11" t="n">
-        <v>1973.065479385524</v>
+        <v>1135.451171271065</v>
       </c>
       <c r="M11" t="n">
-        <v>2453.15</v>
+        <v>1646.3</v>
       </c>
       <c r="N11" t="n">
-        <v>2453.15</v>
+        <v>1646.3</v>
       </c>
       <c r="O11" t="n">
         <v>2453.15</v>
@@ -5065,19 +5065,19 @@
         <v>2622.097222696074</v>
       </c>
       <c r="U11" t="n">
-        <v>2193.590862545962</v>
+        <v>2622.097222696074</v>
       </c>
       <c r="V11" t="n">
-        <v>1784.650434094625</v>
+        <v>2285.206490315848</v>
       </c>
       <c r="W11" t="n">
-        <v>1505.387826703751</v>
+        <v>1867.657524678527</v>
       </c>
       <c r="X11" t="n">
-        <v>1134.39607573338</v>
+        <v>1496.665773708156</v>
       </c>
       <c r="Y11" t="n">
-        <v>845.1865477709493</v>
+        <v>1207.456245745725</v>
       </c>
     </row>
     <row r="12">
@@ -5126,7 +5126,7 @@
         <v>1990.605502182875</v>
       </c>
       <c r="O12" t="n">
-        <v>2452.397953866594</v>
+        <v>2248.573656412845</v>
       </c>
       <c r="P12" t="n">
         <v>2583.853000882351</v>
@@ -5166,76 +5166,76 @@
         </is>
       </c>
       <c r="B13" t="n">
-        <v>177.5115880782802</v>
+        <v>194.8013510556871</v>
       </c>
       <c r="C13" t="n">
-        <v>177.5115880782802</v>
+        <v>146.5940312091773</v>
       </c>
       <c r="D13" t="n">
-        <v>177.5115880782802</v>
+        <v>85.44633620356569</v>
       </c>
       <c r="E13" t="n">
-        <v>177.5115880782802</v>
+        <v>85.44633620356569</v>
       </c>
       <c r="F13" t="n">
-        <v>177.5115880782802</v>
+        <v>85.44633620356569</v>
       </c>
       <c r="G13" t="n">
-        <v>177.5115880782802</v>
+        <v>65.2</v>
       </c>
       <c r="H13" t="n">
-        <v>173.7023697938169</v>
+        <v>65.2</v>
       </c>
       <c r="I13" t="n">
-        <v>221.5852487298998</v>
+        <v>113.0828789360829</v>
       </c>
       <c r="J13" t="n">
-        <v>409.4189893823511</v>
+        <v>300.9166195885342</v>
       </c>
       <c r="K13" t="n">
-        <v>409.4189893823511</v>
+        <v>300.9166195885342</v>
       </c>
       <c r="L13" t="n">
-        <v>409.4189893823511</v>
+        <v>300.9166195885342</v>
       </c>
       <c r="M13" t="n">
-        <v>409.4189893823511</v>
+        <v>300.9166195885342</v>
       </c>
       <c r="N13" t="n">
-        <v>409.4189893823511</v>
+        <v>300.9166195885342</v>
       </c>
       <c r="O13" t="n">
-        <v>409.4189893823511</v>
+        <v>300.9166195885342</v>
       </c>
       <c r="P13" t="n">
-        <v>409.4189893823511</v>
+        <v>300.9166195885342</v>
       </c>
       <c r="Q13" t="n">
-        <v>65.2</v>
+        <v>300.9166195885342</v>
       </c>
       <c r="R13" t="n">
-        <v>65.2</v>
+        <v>143.8442988343452</v>
       </c>
       <c r="S13" t="n">
-        <v>65.2</v>
+        <v>143.8442988343452</v>
       </c>
       <c r="T13" t="n">
-        <v>80.02567915880486</v>
+        <v>158.6699779931501</v>
       </c>
       <c r="U13" t="n">
-        <v>153.3268717970915</v>
+        <v>231.9711706314367</v>
       </c>
       <c r="V13" t="n">
-        <v>178.8982646830374</v>
+        <v>257.5425635173827</v>
       </c>
       <c r="W13" t="n">
-        <v>177.5115880782802</v>
+        <v>257.5425635173827</v>
       </c>
       <c r="X13" t="n">
-        <v>177.5115880782802</v>
+        <v>257.5425635173827</v>
       </c>
       <c r="Y13" t="n">
-        <v>177.5115880782802</v>
+        <v>257.5425635173827</v>
       </c>
     </row>
     <row r="14">
@@ -5245,22 +5245,22 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>883.6685602764463</v>
+        <v>880.1835184729979</v>
       </c>
       <c r="C14" t="n">
-        <v>711.4720165966545</v>
+        <v>707.9869747932061</v>
       </c>
       <c r="D14" t="n">
-        <v>578.8062027180183</v>
+        <v>575.3211609145699</v>
       </c>
       <c r="E14" t="n">
-        <v>452.1766172565348</v>
+        <v>448.6915754530864</v>
       </c>
       <c r="F14" t="n">
-        <v>325.0153761373309</v>
+        <v>321.5303343338825</v>
       </c>
       <c r="G14" t="n">
-        <v>198.9978283726681</v>
+        <v>195.5127865692196</v>
       </c>
       <c r="H14" t="n">
         <v>65.2</v>
@@ -5269,25 +5269,25 @@
         <v>65.2</v>
       </c>
       <c r="J14" t="n">
-        <v>456.5091130376557</v>
+        <v>65.2</v>
       </c>
       <c r="K14" t="n">
-        <v>1166.215479385524</v>
+        <v>774.9063663478685</v>
       </c>
       <c r="L14" t="n">
-        <v>1973.065479385524</v>
+        <v>774.9063663478685</v>
       </c>
       <c r="M14" t="n">
-        <v>2483.914308114459</v>
+        <v>1285.755195076803</v>
       </c>
       <c r="N14" t="n">
-        <v>3097.134627889222</v>
+        <v>1898.975514851566</v>
       </c>
       <c r="O14" t="n">
-        <v>3097.134627889222</v>
+        <v>2014.550904947333</v>
       </c>
       <c r="P14" t="n">
-        <v>3097.134627889222</v>
+        <v>2821.400904947332</v>
       </c>
       <c r="Q14" t="n">
         <v>3260</v>
@@ -5308,13 +5308,13 @@
         <v>2002.832252276443</v>
       </c>
       <c r="W14" t="n">
-        <v>1639.828741184576</v>
+        <v>1636.343699381128</v>
       </c>
       <c r="X14" t="n">
-        <v>1323.382444759659</v>
+        <v>1319.897402956211</v>
       </c>
       <c r="Y14" t="n">
-        <v>1088.718371342683</v>
+        <v>1085.233329539235</v>
       </c>
     </row>
     <row r="15">
@@ -5345,28 +5345,28 @@
         <v>65.2</v>
       </c>
       <c r="I15" t="n">
-        <v>126.454877967565</v>
+        <v>65.2</v>
       </c>
       <c r="J15" t="n">
-        <v>404.5252825072959</v>
+        <v>189.156520175299</v>
       </c>
       <c r="K15" t="n">
-        <v>593.7180986016792</v>
+        <v>654.5593362696824</v>
       </c>
       <c r="L15" t="n">
-        <v>865.0685601968793</v>
+        <v>925.9097978648824</v>
       </c>
       <c r="M15" t="n">
-        <v>951.1491019397386</v>
+        <v>1288.200339607742</v>
       </c>
       <c r="N15" t="n">
-        <v>1360.639386547307</v>
+        <v>1465.500914107732</v>
       </c>
       <c r="O15" t="n">
-        <v>1599.681838231026</v>
+        <v>1704.543365791451</v>
       </c>
       <c r="P15" t="n">
-        <v>1712.211182700533</v>
+        <v>1817.072710260958</v>
       </c>
       <c r="Q15" t="n">
         <v>1817.072710260958</v>
@@ -5433,22 +5433,22 @@
         <v>859.3827230120968</v>
       </c>
       <c r="L16" t="n">
-        <v>859.3827230120968</v>
+        <v>713.3750178022188</v>
       </c>
       <c r="M16" t="n">
-        <v>859.3827230120968</v>
+        <v>713.3750178022188</v>
       </c>
       <c r="N16" t="n">
-        <v>859.3827230120968</v>
+        <v>430.2965293727424</v>
       </c>
       <c r="O16" t="n">
-        <v>859.3827230120968</v>
+        <v>65.2</v>
       </c>
       <c r="P16" t="n">
-        <v>446.80908934717</v>
+        <v>65.2</v>
       </c>
       <c r="Q16" t="n">
-        <v>446.80908934717</v>
+        <v>65.2</v>
       </c>
       <c r="R16" t="n">
         <v>65.2</v>
@@ -5512,10 +5512,10 @@
         <v>1166.215479385524</v>
       </c>
       <c r="L17" t="n">
-        <v>1973.065479385524</v>
+        <v>1697.331756443634</v>
       </c>
       <c r="M17" t="n">
-        <v>2483.914308114459</v>
+        <v>2208.180585172569</v>
       </c>
       <c r="N17" t="n">
         <v>2821.400904947332</v>
@@ -5530,7 +5530,7 @@
         <v>3260</v>
       </c>
       <c r="R17" t="n">
-        <v>3260</v>
+        <v>3256.514958196551</v>
       </c>
       <c r="S17" t="n">
         <v>3038.486505870972</v>
@@ -5582,28 +5582,28 @@
         <v>65.2</v>
       </c>
       <c r="I18" t="n">
-        <v>126.454877967565</v>
+        <v>65.2</v>
       </c>
       <c r="J18" t="n">
-        <v>526.6213981428639</v>
+        <v>465.3665201752989</v>
       </c>
       <c r="K18" t="n">
-        <v>869.9280986016793</v>
+        <v>654.5593362696823</v>
       </c>
       <c r="L18" t="n">
-        <v>1141.278560196879</v>
+        <v>925.9097978648824</v>
       </c>
       <c r="M18" t="n">
-        <v>1227.359101939739</v>
+        <v>1011.990339607742</v>
       </c>
       <c r="N18" t="n">
-        <v>1360.639386547307</v>
+        <v>1145.27062421531</v>
       </c>
       <c r="O18" t="n">
-        <v>1599.681838231026</v>
+        <v>1660.523075899029</v>
       </c>
       <c r="P18" t="n">
-        <v>1712.211182700533</v>
+        <v>1817.072710260958</v>
       </c>
       <c r="Q18" t="n">
         <v>1817.072710260958</v>
@@ -5679,16 +5679,16 @@
         <v>859.3827230120968</v>
       </c>
       <c r="O19" t="n">
-        <v>859.3827230120968</v>
+        <v>494.2861936393544</v>
       </c>
       <c r="P19" t="n">
-        <v>516.552794369291</v>
+        <v>494.2861936393544</v>
       </c>
       <c r="Q19" t="n">
-        <v>65.2</v>
+        <v>494.2861936393544</v>
       </c>
       <c r="R19" t="n">
-        <v>65.2</v>
+        <v>149.4156360634904</v>
       </c>
       <c r="S19" t="n">
         <v>65.2</v>
@@ -5737,28 +5737,28 @@
         <v>198.9978283726681</v>
       </c>
       <c r="H20" t="n">
-        <v>68.68504180344846</v>
+        <v>65.2</v>
       </c>
       <c r="I20" t="n">
         <v>65.2</v>
       </c>
       <c r="J20" t="n">
-        <v>180.775390095766</v>
+        <v>65.2</v>
       </c>
       <c r="K20" t="n">
-        <v>890.4817564436344</v>
+        <v>774.9063663478685</v>
       </c>
       <c r="L20" t="n">
-        <v>1697.331756443634</v>
+        <v>774.9063663478685</v>
       </c>
       <c r="M20" t="n">
-        <v>2208.180585172569</v>
+        <v>774.9063663478685</v>
       </c>
       <c r="N20" t="n">
-        <v>2821.400904947332</v>
+        <v>1388.126686122632</v>
       </c>
       <c r="O20" t="n">
-        <v>2821.400904947332</v>
+        <v>2194.976686122632</v>
       </c>
       <c r="P20" t="n">
         <v>2821.400904947332</v>
@@ -5819,28 +5819,28 @@
         <v>65.2</v>
       </c>
       <c r="I21" t="n">
-        <v>126.454877967565</v>
+        <v>65.2</v>
       </c>
       <c r="J21" t="n">
-        <v>250.4113981428639</v>
+        <v>189.156520175299</v>
       </c>
       <c r="K21" t="n">
-        <v>439.6042142372473</v>
+        <v>378.3493362696823</v>
       </c>
       <c r="L21" t="n">
-        <v>710.9546758324475</v>
+        <v>649.6997978648824</v>
       </c>
       <c r="M21" t="n">
-        <v>797.0352175753068</v>
+        <v>1011.990339607742</v>
       </c>
       <c r="N21" t="n">
-        <v>1084.429386547307</v>
+        <v>1421.48062421531</v>
       </c>
       <c r="O21" t="n">
-        <v>1323.471838231026</v>
+        <v>1660.523075899029</v>
       </c>
       <c r="P21" t="n">
-        <v>1712.211182700533</v>
+        <v>1817.072710260958</v>
       </c>
       <c r="Q21" t="n">
         <v>1817.072710260958</v>
@@ -5877,55 +5877,55 @@
         </is>
       </c>
       <c r="B22" t="n">
-        <v>422.6199739669084</v>
+        <v>414.4242160506674</v>
       </c>
       <c r="C22" t="n">
-        <v>428.8319797853442</v>
+        <v>420.6362218691032</v>
       </c>
       <c r="D22" t="n">
-        <v>428.8319797853442</v>
+        <v>414.0339814089461</v>
       </c>
       <c r="E22" t="n">
-        <v>428.8319797853442</v>
+        <v>414.0339814089461</v>
       </c>
       <c r="F22" t="n">
-        <v>433.4029523772797</v>
+        <v>418.6049540008816</v>
       </c>
       <c r="G22" t="n">
-        <v>467.019518264165</v>
+        <v>452.2215198877669</v>
       </c>
       <c r="H22" t="n">
-        <v>516.7461034235625</v>
+        <v>501.9481050471645</v>
       </c>
       <c r="I22" t="n">
-        <v>618.0889823596455</v>
+        <v>603.2909839832473</v>
       </c>
       <c r="J22" t="n">
-        <v>859.3827230120968</v>
+        <v>844.5847246356986</v>
       </c>
       <c r="K22" t="n">
-        <v>859.3827230120968</v>
+        <v>844.5847246356986</v>
       </c>
       <c r="L22" t="n">
-        <v>859.3827230120968</v>
+        <v>844.5847246356986</v>
       </c>
       <c r="M22" t="n">
-        <v>859.3827230120968</v>
+        <v>844.5847246356986</v>
       </c>
       <c r="N22" t="n">
-        <v>859.3827230120968</v>
+        <v>844.5847246356986</v>
       </c>
       <c r="O22" t="n">
-        <v>494.2861936393544</v>
+        <v>844.5847246356986</v>
       </c>
       <c r="P22" t="n">
-        <v>494.2861936393544</v>
+        <v>432.0110909707719</v>
       </c>
       <c r="Q22" t="n">
-        <v>494.2861936393544</v>
+        <v>432.0110909707719</v>
       </c>
       <c r="R22" t="n">
-        <v>65.2</v>
+        <v>149.4156360634904</v>
       </c>
       <c r="S22" t="n">
         <v>65.2</v>
@@ -5971,10 +5971,10 @@
         <v>325.0153761373309</v>
       </c>
       <c r="G23" t="n">
-        <v>198.9978283726681</v>
+        <v>195.5127865692196</v>
       </c>
       <c r="H23" t="n">
-        <v>68.68504180344846</v>
+        <v>65.2</v>
       </c>
       <c r="I23" t="n">
         <v>65.2</v>
@@ -5986,19 +5986,19 @@
         <v>1166.215479385524</v>
       </c>
       <c r="L23" t="n">
-        <v>1697.331756443634</v>
+        <v>1973.065479385524</v>
       </c>
       <c r="M23" t="n">
-        <v>2208.180585172569</v>
+        <v>1973.065479385524</v>
       </c>
       <c r="N23" t="n">
-        <v>2821.400904947332</v>
+        <v>2586.285799160287</v>
       </c>
       <c r="O23" t="n">
-        <v>2821.400904947332</v>
+        <v>3260</v>
       </c>
       <c r="P23" t="n">
-        <v>2821.400904947332</v>
+        <v>3260</v>
       </c>
       <c r="Q23" t="n">
         <v>3260</v>
@@ -6059,25 +6059,25 @@
         <v>65.2</v>
       </c>
       <c r="J24" t="n">
-        <v>404.5252825072959</v>
+        <v>189.156520175299</v>
       </c>
       <c r="K24" t="n">
-        <v>869.9280986016793</v>
+        <v>378.3493362696823</v>
       </c>
       <c r="L24" t="n">
-        <v>1141.278560196879</v>
+        <v>925.9097978648825</v>
       </c>
       <c r="M24" t="n">
-        <v>1227.359101939739</v>
+        <v>1056.010629500164</v>
       </c>
       <c r="N24" t="n">
-        <v>1360.639386547307</v>
+        <v>1189.290914107732</v>
       </c>
       <c r="O24" t="n">
-        <v>1599.681838231026</v>
+        <v>1704.543365791451</v>
       </c>
       <c r="P24" t="n">
-        <v>1712.211182700533</v>
+        <v>1817.072710260958</v>
       </c>
       <c r="Q24" t="n">
         <v>1817.072710260958</v>
@@ -6120,43 +6120,43 @@
         <v>428.8319797853442</v>
       </c>
       <c r="D25" t="n">
-        <v>428.8319797853442</v>
+        <v>422.2297393251872</v>
       </c>
       <c r="E25" t="n">
-        <v>428.8319797853442</v>
+        <v>422.2297393251872</v>
       </c>
       <c r="F25" t="n">
-        <v>433.4029523772797</v>
+        <v>426.8007119171227</v>
       </c>
       <c r="G25" t="n">
-        <v>467.019518264165</v>
+        <v>460.4172778040079</v>
       </c>
       <c r="H25" t="n">
-        <v>516.7461034235625</v>
+        <v>510.1438629634055</v>
       </c>
       <c r="I25" t="n">
-        <v>618.0889823596455</v>
+        <v>611.4867418994884</v>
       </c>
       <c r="J25" t="n">
-        <v>859.3827230120968</v>
+        <v>852.7804825519397</v>
       </c>
       <c r="K25" t="n">
-        <v>859.3827230120968</v>
+        <v>852.7804825519397</v>
       </c>
       <c r="L25" t="n">
-        <v>859.3827230120968</v>
+        <v>761.3956963471728</v>
       </c>
       <c r="M25" t="n">
-        <v>859.3827230120968</v>
+        <v>517.3233615971224</v>
       </c>
       <c r="N25" t="n">
-        <v>859.3827230120968</v>
+        <v>517.3233615971224</v>
       </c>
       <c r="O25" t="n">
-        <v>859.3827230120968</v>
+        <v>517.3233615971224</v>
       </c>
       <c r="P25" t="n">
-        <v>859.3827230120968</v>
+        <v>517.3233615971224</v>
       </c>
       <c r="Q25" t="n">
         <v>517.3233615971224</v>
@@ -6193,19 +6193,19 @@
         </is>
       </c>
       <c r="B26" t="n">
-        <v>705.6712852464632</v>
+        <v>1022.869550081067</v>
       </c>
       <c r="C26" t="n">
-        <v>478.9292870212168</v>
+        <v>796.1275518558203</v>
       </c>
       <c r="D26" t="n">
-        <v>291.718018597126</v>
+        <v>608.9162834317297</v>
       </c>
       <c r="E26" t="n">
-        <v>291.718018597126</v>
+        <v>427.7412434247915</v>
       </c>
       <c r="F26" t="n">
-        <v>247.1782411146742</v>
+        <v>427.7412434247915</v>
       </c>
       <c r="G26" t="n">
         <v>247.1782411146742</v>
@@ -6217,22 +6217,22 @@
         <v>62.32</v>
       </c>
       <c r="J26" t="n">
-        <v>453.6291130376557</v>
+        <v>62.32</v>
       </c>
       <c r="K26" t="n">
-        <v>453.6291130376557</v>
+        <v>62.32</v>
       </c>
       <c r="L26" t="n">
-        <v>453.6291130376557</v>
+        <v>833.53</v>
       </c>
       <c r="M26" t="n">
-        <v>964.4779417665907</v>
+        <v>1344.378828728935</v>
       </c>
       <c r="N26" t="n">
-        <v>1577.698261541354</v>
+        <v>1344.378828728935</v>
       </c>
       <c r="O26" t="n">
-        <v>2348.908261541379</v>
+        <v>1906.190904947332</v>
       </c>
       <c r="P26" t="n">
         <v>2677.400904947332</v>
@@ -6250,19 +6250,19 @@
         <v>2451.957223879615</v>
       </c>
       <c r="U26" t="n">
-        <v>2451.957223879615</v>
+        <v>2023.450863729503</v>
       </c>
       <c r="V26" t="n">
-        <v>2043.016795428278</v>
+        <v>2023.450863729503</v>
       </c>
       <c r="W26" t="n">
-        <v>1625.467829790957</v>
+        <v>1605.901898092182</v>
       </c>
       <c r="X26" t="n">
-        <v>1254.476078820585</v>
+        <v>1571.674343655189</v>
       </c>
       <c r="Y26" t="n">
-        <v>965.2665508581547</v>
+        <v>1282.464815692758</v>
       </c>
     </row>
     <row r="27">
@@ -6302,16 +6302,16 @@
         <v>828.7642142372474</v>
       </c>
       <c r="L27" t="n">
-        <v>1322.864675832448</v>
+        <v>1119.040378378698</v>
       </c>
       <c r="M27" t="n">
-        <v>1631.695217575307</v>
+        <v>1427.870920121557</v>
       </c>
       <c r="N27" t="n">
-        <v>1987.725502182875</v>
+        <v>1783.901204729126</v>
       </c>
       <c r="O27" t="n">
-        <v>2449.517953866594</v>
+        <v>2245.693656412845</v>
       </c>
       <c r="P27" t="n">
         <v>2580.973000882351</v>
@@ -6351,52 +6351,52 @@
         </is>
       </c>
       <c r="B28" t="n">
-        <v>174.6315880782802</v>
+        <v>113.2770522213418</v>
       </c>
       <c r="C28" t="n">
-        <v>174.6315880782802</v>
+        <v>113.2770522213418</v>
       </c>
       <c r="D28" t="n">
-        <v>174.6315880782802</v>
+        <v>113.2770522213418</v>
       </c>
       <c r="E28" t="n">
-        <v>174.6315880782802</v>
+        <v>113.2770522213418</v>
       </c>
       <c r="F28" t="n">
-        <v>174.6315880782802</v>
+        <v>66.12921828446325</v>
       </c>
       <c r="G28" t="n">
-        <v>174.6315880782802</v>
+        <v>66.12921828446325</v>
       </c>
       <c r="H28" t="n">
-        <v>170.8223697938169</v>
+        <v>62.32</v>
       </c>
       <c r="I28" t="n">
-        <v>218.7052487298998</v>
+        <v>110.2028789360829</v>
       </c>
       <c r="J28" t="n">
-        <v>406.5389893823511</v>
+        <v>298.0366195885342</v>
       </c>
       <c r="K28" t="n">
-        <v>406.5389893823511</v>
+        <v>298.0366195885342</v>
       </c>
       <c r="L28" t="n">
-        <v>406.5389893823511</v>
+        <v>298.0366195885342</v>
       </c>
       <c r="M28" t="n">
-        <v>406.5389893823511</v>
+        <v>298.0366195885342</v>
       </c>
       <c r="N28" t="n">
-        <v>406.5389893823511</v>
+        <v>298.0366195885342</v>
       </c>
       <c r="O28" t="n">
-        <v>406.5389893823511</v>
+        <v>298.0366195885342</v>
       </c>
       <c r="P28" t="n">
-        <v>406.5389893823511</v>
+        <v>298.0366195885342</v>
       </c>
       <c r="Q28" t="n">
-        <v>406.5389893823511</v>
+        <v>298.0366195885342</v>
       </c>
       <c r="R28" t="n">
         <v>62.32</v>
@@ -6414,13 +6414,13 @@
         <v>176.0182646830374</v>
       </c>
       <c r="W28" t="n">
-        <v>174.6315880782802</v>
+        <v>176.0182646830374</v>
       </c>
       <c r="X28" t="n">
-        <v>174.6315880782802</v>
+        <v>176.0182646830374</v>
       </c>
       <c r="Y28" t="n">
-        <v>174.6315880782802</v>
+        <v>176.0182646830374</v>
       </c>
     </row>
     <row r="29">
@@ -6430,22 +6430,22 @@
         </is>
       </c>
       <c r="B29" t="n">
-        <v>513.4059340138206</v>
+        <v>888.4048733179196</v>
       </c>
       <c r="C29" t="n">
-        <v>312.9265620512004</v>
+        <v>687.9255013552995</v>
       </c>
       <c r="D29" t="n">
-        <v>151.977919889736</v>
+        <v>526.976859193835</v>
       </c>
       <c r="E29" t="n">
-        <v>151.977919889736</v>
+        <v>372.0644454495233</v>
       </c>
       <c r="F29" t="n">
-        <v>151.977919889736</v>
+        <v>216.6203760474911</v>
       </c>
       <c r="G29" t="n">
-        <v>151.977919889736</v>
+        <v>62.32</v>
       </c>
       <c r="H29" t="n">
         <v>62.32</v>
@@ -6457,19 +6457,19 @@
         <v>453.6291130376557</v>
       </c>
       <c r="K29" t="n">
-        <v>453.6291130376557</v>
+        <v>1163.335479385524</v>
       </c>
       <c r="L29" t="n">
-        <v>453.6291130376557</v>
+        <v>1163.335479385524</v>
       </c>
       <c r="M29" t="n">
-        <v>964.4779417665907</v>
+        <v>1292.970585172569</v>
       </c>
       <c r="N29" t="n">
-        <v>1134.980904947268</v>
+        <v>1906.190904947332</v>
       </c>
       <c r="O29" t="n">
-        <v>1906.1909049473</v>
+        <v>2677.400904947332</v>
       </c>
       <c r="P29" t="n">
         <v>2677.400904947332</v>
@@ -6487,19 +6487,19 @@
         <v>2530.622475221327</v>
       </c>
       <c r="U29" t="n">
-        <v>2128.378741333841</v>
+        <v>2503.37768063794</v>
       </c>
       <c r="V29" t="n">
-        <v>1745.70093914513</v>
+        <v>2120.699878449229</v>
       </c>
       <c r="W29" t="n">
-        <v>1354.414599770435</v>
+        <v>1729.413539074535</v>
       </c>
       <c r="X29" t="n">
-        <v>1009.68547506269</v>
+        <v>1384.684414366789</v>
       </c>
       <c r="Y29" t="n">
-        <v>746.7385733628857</v>
+        <v>1121.737512666985</v>
       </c>
     </row>
     <row r="30">
@@ -6533,25 +6533,25 @@
         <v>95.85487796756496</v>
       </c>
       <c r="J30" t="n">
-        <v>468.3013981428639</v>
+        <v>461.4892343101459</v>
       </c>
       <c r="K30" t="n">
-        <v>657.4942142372473</v>
+        <v>650.6820504045293</v>
       </c>
       <c r="L30" t="n">
-        <v>928.8446758324474</v>
+        <v>922.0325119997293</v>
       </c>
       <c r="M30" t="n">
-        <v>1014.925217575307</v>
+        <v>1008.113053742589</v>
       </c>
       <c r="N30" t="n">
-        <v>1396.695502182875</v>
+        <v>1389.883338350157</v>
       </c>
       <c r="O30" t="n">
-        <v>1800.27426247345</v>
+        <v>1877.415790033876</v>
       </c>
       <c r="P30" t="n">
-        <v>2161.293606942957</v>
+        <v>2238.435134503382</v>
       </c>
       <c r="Q30" t="n">
         <v>2238.435134503382</v>
@@ -6627,13 +6627,13 @@
         <v>596.2397446017254</v>
       </c>
       <c r="O31" t="n">
-        <v>202.8603869461547</v>
+        <v>596.2397446017254</v>
       </c>
       <c r="P31" t="n">
-        <v>62.32</v>
+        <v>542.7261898799507</v>
       </c>
       <c r="Q31" t="n">
-        <v>62.32</v>
+        <v>542.7261898799507</v>
       </c>
       <c r="R31" t="n">
         <v>62.32</v>
@@ -6697,19 +6697,19 @@
         <v>772.0263663478684</v>
       </c>
       <c r="L32" t="n">
-        <v>1292.970585172523</v>
+        <v>1543.236366347868</v>
       </c>
       <c r="M32" t="n">
-        <v>1292.970585172523</v>
+        <v>2054.085195076803</v>
       </c>
       <c r="N32" t="n">
-        <v>1906.190904947286</v>
+        <v>2054.085195076803</v>
       </c>
       <c r="O32" t="n">
-        <v>2677.400904947332</v>
+        <v>2005.763355153865</v>
       </c>
       <c r="P32" t="n">
-        <v>2677.400904947332</v>
+        <v>2776.973355153865</v>
       </c>
       <c r="Q32" t="n">
         <v>3116</v>
@@ -6718,22 +6718,22 @@
         <v>3116</v>
       </c>
       <c r="S32" t="n">
-        <v>2917.424687689154</v>
+        <v>2907.06245676533</v>
       </c>
       <c r="T32" t="n">
-        <v>2615.732180892625</v>
+        <v>2605.369949968801</v>
       </c>
       <c r="U32" t="n">
-        <v>2250.862184378877</v>
+        <v>2240.499953455053</v>
       </c>
       <c r="V32" t="n">
-        <v>1905.558119563903</v>
+        <v>1895.195888640079</v>
       </c>
       <c r="W32" t="n">
-        <v>1551.645517562946</v>
+        <v>1541.283286639122</v>
       </c>
       <c r="X32" t="n">
-        <v>1244.290130228938</v>
+        <v>1233.927899305114</v>
       </c>
       <c r="Y32" t="n">
         <v>1018.716965902871</v>
@@ -6770,25 +6770,25 @@
         <v>62.32</v>
       </c>
       <c r="J33" t="n">
-        <v>186.2765201752989</v>
+        <v>361.2331737040851</v>
       </c>
       <c r="K33" t="n">
-        <v>375.4693362696823</v>
+        <v>550.4259897984684</v>
       </c>
       <c r="L33" t="n">
-        <v>646.8197978648825</v>
+        <v>821.7764513936685</v>
       </c>
       <c r="M33" t="n">
-        <v>732.9003396077418</v>
+        <v>907.8569931365278</v>
       </c>
       <c r="N33" t="n">
-        <v>866.1806242153101</v>
+        <v>1041.137277744096</v>
       </c>
       <c r="O33" t="n">
-        <v>1166.408201867389</v>
+        <v>1280.179729427815</v>
       </c>
       <c r="P33" t="n">
-        <v>1564.057546336896</v>
+        <v>1677.829073897321</v>
       </c>
       <c r="Q33" t="n">
         <v>1677.829073897321</v>
@@ -6855,19 +6855,19 @@
         <v>965.3074096938342</v>
       </c>
       <c r="L34" t="n">
-        <v>965.3074096938342</v>
+        <v>828.3906135748653</v>
       </c>
       <c r="M34" t="n">
-        <v>965.3074096938342</v>
+        <v>828.3906135748653</v>
       </c>
       <c r="N34" t="n">
-        <v>965.3074096938342</v>
+        <v>821.8083448558509</v>
       </c>
       <c r="O34" t="n">
-        <v>609.3017894120009</v>
+        <v>465.8027245740176</v>
       </c>
       <c r="P34" t="n">
-        <v>205.8190648379832</v>
+        <v>62.32</v>
       </c>
       <c r="Q34" t="n">
         <v>62.32</v>
@@ -6904,22 +6904,22 @@
         </is>
       </c>
       <c r="B35" t="n">
-        <v>812.3958330040078</v>
+        <v>822.7580639275434</v>
       </c>
       <c r="C35" t="n">
-        <v>649.2901984151251</v>
+        <v>659.6524293386606</v>
       </c>
       <c r="D35" t="n">
-        <v>525.7152936273981</v>
+        <v>536.0775245509335</v>
       </c>
       <c r="E35" t="n">
-        <v>408.1766172568236</v>
+        <v>418.5388481803591</v>
       </c>
       <c r="F35" t="n">
-        <v>290.1062852285288</v>
+        <v>300.4685161520642</v>
       </c>
       <c r="G35" t="n">
-        <v>173.179646554775</v>
+        <v>183.5418774783105</v>
       </c>
       <c r="H35" t="n">
         <v>62.32</v>
@@ -6931,49 +6931,49 @@
         <v>453.6291130376557</v>
       </c>
       <c r="K35" t="n">
-        <v>453.6291130376557</v>
+        <v>1163.335479385524</v>
       </c>
       <c r="L35" t="n">
-        <v>453.6291130376557</v>
+        <v>1621.901839922923</v>
       </c>
       <c r="M35" t="n">
-        <v>964.4779417665907</v>
+        <v>1621.901839922923</v>
       </c>
       <c r="N35" t="n">
-        <v>1576.736656926695</v>
+        <v>1573.58</v>
       </c>
       <c r="O35" t="n">
-        <v>1906.190904947263</v>
+        <v>2344.79</v>
       </c>
       <c r="P35" t="n">
-        <v>2677.400904947332</v>
+        <v>3116</v>
       </c>
       <c r="Q35" t="n">
         <v>3116</v>
       </c>
       <c r="R35" t="n">
-        <v>3116.000000000288</v>
+        <v>3116</v>
       </c>
       <c r="S35" t="n">
-        <v>2907.062456765618</v>
+        <v>2907.06245676533</v>
       </c>
       <c r="T35" t="n">
-        <v>2605.369949969089</v>
+        <v>2605.369949968801</v>
       </c>
       <c r="U35" t="n">
-        <v>2240.499953455341</v>
+        <v>2250.862184378877</v>
       </c>
       <c r="V35" t="n">
-        <v>1895.195888640368</v>
+        <v>1905.558119563903</v>
       </c>
       <c r="W35" t="n">
-        <v>1541.283286639411</v>
+        <v>1551.645517562946</v>
       </c>
       <c r="X35" t="n">
-        <v>1233.927899305403</v>
+        <v>1244.290130228938</v>
       </c>
       <c r="Y35" t="n">
-        <v>1008.354734979336</v>
+        <v>1018.716965902871</v>
       </c>
     </row>
     <row r="36">
@@ -7013,19 +7013,19 @@
         <v>375.4693362696823</v>
       </c>
       <c r="L36" t="n">
-        <v>646.8197978648825</v>
+        <v>821.7764513936683</v>
       </c>
       <c r="M36" t="n">
-        <v>794.0854655761023</v>
+        <v>907.8569931365275</v>
       </c>
       <c r="N36" t="n">
-        <v>927.3657501836706</v>
+        <v>1041.137277744096</v>
       </c>
       <c r="O36" t="n">
-        <v>1451.528201867389</v>
+        <v>1565.299729427815</v>
       </c>
       <c r="P36" t="n">
-        <v>1564.057546336896</v>
+        <v>1677.829073897321</v>
       </c>
       <c r="Q36" t="n">
         <v>1677.829073897321</v>
@@ -7095,16 +7095,16 @@
         <v>828.3906135748653</v>
       </c>
       <c r="M37" t="n">
-        <v>593.4091879157239</v>
+        <v>828.3906135748653</v>
       </c>
       <c r="N37" t="n">
-        <v>593.4091879157239</v>
+        <v>828.3906135748653</v>
       </c>
       <c r="O37" t="n">
-        <v>593.4091879157239</v>
+        <v>828.3906135748653</v>
       </c>
       <c r="P37" t="n">
-        <v>593.4091879157239</v>
+        <v>828.3906135748653</v>
       </c>
       <c r="Q37" t="n">
         <v>580.4771794787945</v>
@@ -7168,16 +7168,16 @@
         <v>453.6291130376557</v>
       </c>
       <c r="K38" t="n">
-        <v>1162.930063016384</v>
+        <v>1162.373874771057</v>
       </c>
       <c r="L38" t="n">
-        <v>1906.190904947241</v>
+        <v>1933.583874771057</v>
       </c>
       <c r="M38" t="n">
-        <v>1906.190904947241</v>
+        <v>1933.583874771057</v>
       </c>
       <c r="N38" t="n">
-        <v>1906.190904947241</v>
+        <v>1933.583874771057</v>
       </c>
       <c r="O38" t="n">
         <v>2677.400904947332</v>
@@ -7189,25 +7189,25 @@
         <v>3116</v>
       </c>
       <c r="R38" t="n">
-        <v>3116.000000000375</v>
+        <v>3116</v>
       </c>
       <c r="S38" t="n">
-        <v>2907.062456765706</v>
+        <v>2907.06245676533</v>
       </c>
       <c r="T38" t="n">
-        <v>2605.369949969177</v>
+        <v>2605.369949968801</v>
       </c>
       <c r="U38" t="n">
-        <v>2240.499953455429</v>
+        <v>2240.499953455053</v>
       </c>
       <c r="V38" t="n">
-        <v>1895.195888640455</v>
+        <v>1895.195888640079</v>
       </c>
       <c r="W38" t="n">
-        <v>1541.283286639498</v>
+        <v>1541.283286639122</v>
       </c>
       <c r="X38" t="n">
-        <v>1233.92789930549</v>
+        <v>1233.927899305114</v>
       </c>
       <c r="Y38" t="n">
         <v>1018.716965902871</v>
@@ -7253,13 +7253,13 @@
         <v>646.8197978648825</v>
       </c>
       <c r="M39" t="n">
-        <v>732.9003396077418</v>
+        <v>907.8569931365278</v>
       </c>
       <c r="N39" t="n">
-        <v>866.1806242153101</v>
+        <v>1041.137277744096</v>
       </c>
       <c r="O39" t="n">
-        <v>1390.343075899029</v>
+        <v>1280.179729427815</v>
       </c>
       <c r="P39" t="n">
         <v>1677.829073897321</v>
@@ -7329,25 +7329,25 @@
         <v>965.3074096938342</v>
       </c>
       <c r="L40" t="n">
-        <v>965.3074096938342</v>
+        <v>828.3906135748653</v>
       </c>
       <c r="M40" t="n">
-        <v>965.3074096938342</v>
+        <v>828.3906135748653</v>
       </c>
       <c r="N40" t="n">
-        <v>965.3074096938342</v>
+        <v>828.3906135748653</v>
       </c>
       <c r="O40" t="n">
-        <v>908.0646098523995</v>
+        <v>828.3906135748653</v>
       </c>
       <c r="P40" t="n">
-        <v>504.5818852783818</v>
+        <v>828.3906135748653</v>
       </c>
       <c r="Q40" t="n">
-        <v>62.32</v>
+        <v>580.4771794787945</v>
       </c>
       <c r="R40" t="n">
-        <v>62.32</v>
+        <v>137.4447269725813</v>
       </c>
       <c r="S40" t="n">
         <v>62.32</v>
@@ -7378,16 +7378,16 @@
         </is>
       </c>
       <c r="B41" t="n">
-        <v>277.4812714177045</v>
+        <v>695.6307295572024</v>
       </c>
       <c r="C41" t="n">
-        <v>277.4812714177045</v>
+        <v>695.6307295572024</v>
       </c>
       <c r="D41" t="n">
-        <v>277.4812714177045</v>
+        <v>478.1164308300814</v>
       </c>
       <c r="E41" t="n">
-        <v>277.4812714177045</v>
+        <v>478.1164308300814</v>
       </c>
       <c r="F41" t="n">
         <v>277.4812714177045</v>
@@ -7405,19 +7405,19 @@
         <v>62.32</v>
       </c>
       <c r="K41" t="n">
-        <v>624.13207621812</v>
+        <v>772.0263663478684</v>
       </c>
       <c r="L41" t="n">
-        <v>624.13207621812</v>
+        <v>1543.236366347868</v>
       </c>
       <c r="M41" t="n">
-        <v>1134.980904947055</v>
+        <v>1543.236366347868</v>
       </c>
       <c r="N41" t="n">
-        <v>1134.980904947055</v>
+        <v>2156.456686122632</v>
       </c>
       <c r="O41" t="n">
-        <v>1906.190904947194</v>
+        <v>2677.400904947332</v>
       </c>
       <c r="P41" t="n">
         <v>2677.400904947332</v>
@@ -7429,25 +7429,25 @@
         <v>3059.556970880511</v>
       </c>
       <c r="S41" t="n">
-        <v>3029.723652755073</v>
+        <v>2756.680033706447</v>
       </c>
       <c r="T41" t="n">
-        <v>2634.09175201915</v>
+        <v>2361.048132970524</v>
       </c>
       <c r="U41" t="n">
-        <v>2175.282361566008</v>
+        <v>1902.238742517382</v>
       </c>
       <c r="V41" t="n">
-        <v>1736.03890281164</v>
+        <v>1462.995283763014</v>
       </c>
       <c r="W41" t="n">
-        <v>1288.186906871289</v>
+        <v>1015.143287822663</v>
       </c>
       <c r="X41" t="n">
-        <v>886.8921255978871</v>
+        <v>1015.143287822663</v>
       </c>
       <c r="Y41" t="n">
-        <v>567.3795673324262</v>
+        <v>695.6307295572024</v>
       </c>
     </row>
     <row r="42">
@@ -7484,40 +7484,40 @@
         <v>379.326520175299</v>
       </c>
       <c r="K42" t="n">
-        <v>761.5693362696824</v>
+        <v>670.9295542837699</v>
       </c>
       <c r="L42" t="n">
-        <v>1225.969797864882</v>
+        <v>1135.33001587897</v>
       </c>
       <c r="M42" t="n">
-        <v>1505.100339607742</v>
+        <v>1414.460557621829</v>
       </c>
       <c r="N42" t="n">
-        <v>1699.780494713787</v>
+        <v>1740.790842229397</v>
       </c>
       <c r="O42" t="n">
-        <v>2131.872946397506</v>
+        <v>2172.883293913116</v>
       </c>
       <c r="P42" t="n">
-        <v>2437.452290867013</v>
+        <v>2478.462638382623</v>
       </c>
       <c r="Q42" t="n">
-        <v>2459.153818427438</v>
+        <v>2478.462638382623</v>
       </c>
       <c r="R42" t="n">
-        <v>2459.153818427438</v>
+        <v>2478.462638382623</v>
       </c>
       <c r="S42" t="n">
-        <v>2239.359827154422</v>
+        <v>2478.462638382623</v>
       </c>
       <c r="T42" t="n">
-        <v>2026.87723602562</v>
+        <v>2265.980047253821</v>
       </c>
       <c r="U42" t="n">
-        <v>1819.594044348664</v>
+        <v>2058.696855576865</v>
       </c>
       <c r="V42" t="n">
-        <v>1597.866097690563</v>
+        <v>1836.968908918764</v>
       </c>
       <c r="W42" t="n">
         <v>1597.866097690563</v>
@@ -7536,76 +7536,76 @@
         </is>
       </c>
       <c r="B43" t="n">
-        <v>96.43224858749356</v>
+        <v>62.32</v>
       </c>
       <c r="C43" t="n">
-        <v>96.43224858749356</v>
+        <v>62.32</v>
       </c>
       <c r="D43" t="n">
-        <v>96.43224858749356</v>
+        <v>62.32</v>
       </c>
       <c r="E43" t="n">
-        <v>96.43224858749356</v>
+        <v>62.32</v>
       </c>
       <c r="F43" t="n">
-        <v>96.43224858749356</v>
+        <v>62.32</v>
       </c>
       <c r="G43" t="n">
-        <v>96.43224858749356</v>
+        <v>62.32</v>
       </c>
       <c r="H43" t="n">
         <v>62.32</v>
       </c>
       <c r="I43" t="n">
-        <v>80.50287893608291</v>
+        <v>62.32</v>
       </c>
       <c r="J43" t="n">
-        <v>103.9095272231297</v>
+        <v>113.3984712739228</v>
       </c>
       <c r="K43" t="n">
-        <v>103.9095272231297</v>
+        <v>113.3984712739228</v>
       </c>
       <c r="L43" t="n">
-        <v>103.9095272231297</v>
+        <v>113.3984712739228</v>
       </c>
       <c r="M43" t="n">
-        <v>103.9095272231297</v>
+        <v>113.3984712739228</v>
       </c>
       <c r="N43" t="n">
-        <v>103.9095272231297</v>
+        <v>113.3984712739228</v>
       </c>
       <c r="O43" t="n">
-        <v>103.9095272231297</v>
+        <v>113.3984712739228</v>
       </c>
       <c r="P43" t="n">
-        <v>103.9095272231297</v>
+        <v>113.3984712739228</v>
       </c>
       <c r="Q43" t="n">
-        <v>103.9095272231297</v>
+        <v>113.3984712739228</v>
       </c>
       <c r="R43" t="n">
-        <v>103.9095272231297</v>
+        <v>113.3984712739228</v>
       </c>
       <c r="S43" t="n">
-        <v>103.9095272231297</v>
+        <v>113.3984712739228</v>
       </c>
       <c r="T43" t="n">
-        <v>88.73319741882901</v>
+        <v>98.2221414696221</v>
       </c>
       <c r="U43" t="n">
-        <v>132.3343900571157</v>
+        <v>98.2221414696221</v>
       </c>
       <c r="V43" t="n">
-        <v>128.1219554952811</v>
+        <v>94.00970690778756</v>
       </c>
       <c r="W43" t="n">
-        <v>96.43224858749356</v>
+        <v>62.32</v>
       </c>
       <c r="X43" t="n">
-        <v>96.43224858749356</v>
+        <v>62.32</v>
       </c>
       <c r="Y43" t="n">
-        <v>96.43224858749356</v>
+        <v>62.32</v>
       </c>
     </row>
     <row r="44">
@@ -7615,46 +7615,46 @@
         </is>
       </c>
       <c r="B44" t="n">
-        <v>647.4239578938186</v>
+        <v>1214.479144884835</v>
       </c>
       <c r="C44" t="n">
-        <v>647.4239578938186</v>
+        <v>984.3333977100308</v>
       </c>
       <c r="D44" t="n">
-        <v>647.4239578938186</v>
+        <v>686.0110181748289</v>
       </c>
       <c r="E44" t="n">
-        <v>355.1378067757695</v>
+        <v>393.7248670567798</v>
       </c>
       <c r="F44" t="n">
-        <v>62.32</v>
+        <v>393.7248670567798</v>
       </c>
       <c r="G44" t="n">
-        <v>62.32</v>
+        <v>393.7248670567798</v>
       </c>
       <c r="H44" t="n">
-        <v>62.32</v>
+        <v>97.75551483099457</v>
       </c>
       <c r="I44" t="n">
         <v>62.32</v>
       </c>
       <c r="J44" t="n">
-        <v>453.6291130376557</v>
+        <v>62.32</v>
       </c>
       <c r="K44" t="n">
-        <v>453.6291130376557</v>
+        <v>772.0263663478684</v>
       </c>
       <c r="L44" t="n">
-        <v>453.6291130376557</v>
+        <v>1543.236366347868</v>
       </c>
       <c r="M44" t="n">
-        <v>964.4779417665907</v>
+        <v>2054.085195076803</v>
       </c>
       <c r="N44" t="n">
-        <v>1577.698261541354</v>
+        <v>2344.79</v>
       </c>
       <c r="O44" t="n">
-        <v>2344.789999999806</v>
+        <v>2344.79</v>
       </c>
       <c r="P44" t="n">
         <v>3116</v>
@@ -7672,19 +7672,19 @@
         <v>3116</v>
       </c>
       <c r="U44" t="n">
-        <v>2578.559075359723</v>
+        <v>3116</v>
       </c>
       <c r="V44" t="n">
-        <v>2058.507535797275</v>
+        <v>2595.948460437552</v>
       </c>
       <c r="W44" t="n">
-        <v>1529.847459048843</v>
+        <v>2067.28838368912</v>
       </c>
       <c r="X44" t="n">
-        <v>1047.74459696736</v>
+        <v>1585.185521607637</v>
       </c>
       <c r="Y44" t="n">
-        <v>647.4239578938186</v>
+        <v>1585.185521607637</v>
       </c>
     </row>
     <row r="45">
@@ -7694,25 +7694,25 @@
         </is>
       </c>
       <c r="B45" t="n">
-        <v>62.32</v>
+        <v>1106.231439186222</v>
       </c>
       <c r="C45" t="n">
-        <v>62.32</v>
+        <v>857.6456690392331</v>
       </c>
       <c r="D45" t="n">
-        <v>62.32</v>
+        <v>622.3550762132708</v>
       </c>
       <c r="E45" t="n">
-        <v>62.32</v>
+        <v>392.3832608376014</v>
       </c>
       <c r="F45" t="n">
-        <v>62.32</v>
+        <v>165.4779655468167</v>
       </c>
       <c r="G45" t="n">
-        <v>62.32</v>
+        <v>165.4779655468167</v>
       </c>
       <c r="H45" t="n">
-        <v>62.32</v>
+        <v>165.4779655468167</v>
       </c>
       <c r="I45" t="n">
         <v>62.32</v>
@@ -7721,49 +7721,49 @@
         <v>300.126520175299</v>
       </c>
       <c r="K45" t="n">
-        <v>603.1693362696824</v>
+        <v>545.1702796659088</v>
       </c>
       <c r="L45" t="n">
-        <v>988.3697978648825</v>
+        <v>930.3707412611088</v>
       </c>
       <c r="M45" t="n">
-        <v>1074.450339607742</v>
+        <v>1016.451283003968</v>
       </c>
       <c r="N45" t="n">
-        <v>1308.261043452547</v>
+        <v>1263.581567611536</v>
       </c>
       <c r="O45" t="n">
-        <v>1661.153495136266</v>
+        <v>1616.474019295255</v>
       </c>
       <c r="P45" t="n">
-        <v>1887.532839605772</v>
+        <v>1842.853363764762</v>
       </c>
       <c r="Q45" t="n">
-        <v>1828.866915271954</v>
+        <v>1842.853363764762</v>
       </c>
       <c r="R45" t="n">
-        <v>1392.226715986723</v>
+        <v>1842.853363764762</v>
       </c>
       <c r="S45" t="n">
-        <v>1392.226715986723</v>
+        <v>1686.452950389974</v>
       </c>
       <c r="T45" t="n">
-        <v>1098.93604404984</v>
+        <v>1686.452950389974</v>
       </c>
       <c r="U45" t="n">
-        <v>810.8447715648031</v>
+        <v>1686.452950389974</v>
       </c>
       <c r="V45" t="n">
-        <v>508.308744098621</v>
+        <v>1686.452950389974</v>
       </c>
       <c r="W45" t="n">
-        <v>370.262161055947</v>
+        <v>1686.452950389974</v>
       </c>
       <c r="X45" t="n">
-        <v>62.32</v>
+        <v>1378.510789334027</v>
       </c>
       <c r="Y45" t="n">
-        <v>62.32</v>
+        <v>1378.510789334027</v>
       </c>
     </row>
     <row r="46">
@@ -7797,34 +7797,34 @@
         <v>62.32</v>
       </c>
       <c r="J46" t="n">
-        <v>62.32</v>
+        <v>141.2537406524513</v>
       </c>
       <c r="K46" t="n">
-        <v>62.32</v>
+        <v>141.2537406524513</v>
       </c>
       <c r="L46" t="n">
-        <v>62.32</v>
+        <v>141.2537406524513</v>
       </c>
       <c r="M46" t="n">
-        <v>62.32</v>
+        <v>141.2537406524513</v>
       </c>
       <c r="N46" t="n">
-        <v>62.32</v>
+        <v>141.2537406524513</v>
       </c>
       <c r="O46" t="n">
-        <v>62.32</v>
+        <v>141.2537406524513</v>
       </c>
       <c r="P46" t="n">
-        <v>62.32</v>
+        <v>141.2537406524513</v>
       </c>
       <c r="Q46" t="n">
-        <v>62.32</v>
+        <v>141.2537406524513</v>
       </c>
       <c r="R46" t="n">
-        <v>62.32</v>
+        <v>141.2537406524513</v>
       </c>
       <c r="S46" t="n">
-        <v>62.32</v>
+        <v>141.2537406524513</v>
       </c>
       <c r="T46" t="n">
         <v>62.32</v>
@@ -7967,7 +7967,7 @@
         <v>430.3047365861567</v>
       </c>
       <c r="K2" t="n">
-        <v>503.2488834659004</v>
+        <v>716.8751175230994</v>
       </c>
       <c r="L2" t="n">
         <v>0</v>
@@ -7979,13 +7979,13 @@
         <v>1096.663422488788</v>
       </c>
       <c r="O2" t="n">
-        <v>70.24786957409242</v>
+        <v>283.4325244589817</v>
       </c>
       <c r="P2" t="n">
         <v>815.2870600406815</v>
       </c>
       <c r="Q2" t="n">
-        <v>615.8520732695737</v>
+        <v>189.0411843274853</v>
       </c>
       <c r="R2" t="n">
         <v>294.54111633436</v>
@@ -8204,13 +8204,13 @@
         <v>51.26150624509023</v>
       </c>
       <c r="K5" t="n">
-        <v>67.29211380696711</v>
+        <v>583.3010317149821</v>
       </c>
       <c r="L5" t="n">
         <v>0</v>
       </c>
       <c r="M5" t="n">
-        <v>1060.271045550332</v>
+        <v>544.2621276423173</v>
       </c>
       <c r="N5" t="n">
         <v>1096.663422488788</v>
@@ -8438,22 +8438,22 @@
         <v>120.6470157237802</v>
       </c>
       <c r="J8" t="n">
-        <v>51.26150624509023</v>
+        <v>430.3047365861567</v>
       </c>
       <c r="K8" t="n">
         <v>716.8751175230994</v>
       </c>
       <c r="L8" t="n">
-        <v>165.4169962838677</v>
+        <v>0</v>
       </c>
       <c r="M8" t="n">
-        <v>1060.271045550332</v>
+        <v>544.2621276423173</v>
       </c>
       <c r="N8" t="n">
         <v>1096.663422488788</v>
       </c>
       <c r="O8" t="n">
-        <v>70.24786957409242</v>
+        <v>372.630553424909</v>
       </c>
       <c r="P8" t="n">
         <v>815.2870600406815</v>
@@ -8678,19 +8678,19 @@
         <v>430.3047365861567</v>
       </c>
       <c r="K11" t="n">
-        <v>716.8751175230994</v>
+        <v>0</v>
       </c>
       <c r="L11" t="n">
-        <v>815</v>
+        <v>685.8000588216257</v>
       </c>
       <c r="M11" t="n">
-        <v>1029.195986848859</v>
+        <v>1060.271045550332</v>
       </c>
       <c r="N11" t="n">
         <v>477.2489580698352</v>
       </c>
       <c r="O11" t="n">
-        <v>70.24786957409245</v>
+        <v>885.2478695740924</v>
       </c>
       <c r="P11" t="n">
         <v>815.2870600406815</v>
@@ -8912,13 +8912,13 @@
         <v>120.6470157237802</v>
       </c>
       <c r="J14" t="n">
-        <v>430.3047365861567</v>
+        <v>35.04300624509033</v>
       </c>
       <c r="K14" t="n">
         <v>716.8751175230994</v>
       </c>
       <c r="L14" t="n">
-        <v>815</v>
+        <v>0</v>
       </c>
       <c r="M14" t="n">
         <v>1060.271045550332</v>
@@ -8927,13 +8927,13 @@
         <v>1096.663422488788</v>
       </c>
       <c r="O14" t="n">
-        <v>70.24786957409245</v>
+        <v>186.9906878526441</v>
       </c>
       <c r="P14" t="n">
-        <v>0.2870600406814136</v>
+        <v>815.2870600406815</v>
       </c>
       <c r="Q14" t="n">
-        <v>337.3331612070587</v>
+        <v>615.8520732695737</v>
       </c>
       <c r="R14" t="n">
         <v>294.54111633436</v>
@@ -9155,13 +9155,13 @@
         <v>716.8751175230994</v>
       </c>
       <c r="L17" t="n">
-        <v>815</v>
+        <v>536.481087937485</v>
       </c>
       <c r="M17" t="n">
         <v>1060.271045550332</v>
       </c>
       <c r="N17" t="n">
-        <v>818.1445104262727</v>
+        <v>1096.663422488788</v>
       </c>
       <c r="O17" t="n">
         <v>70.24786957409245</v>
@@ -9386,25 +9386,25 @@
         <v>120.6470157237802</v>
       </c>
       <c r="J20" t="n">
-        <v>151.7858245236418</v>
+        <v>35.04300624509033</v>
       </c>
       <c r="K20" t="n">
         <v>716.8751175230994</v>
       </c>
       <c r="L20" t="n">
-        <v>815</v>
+        <v>0</v>
       </c>
       <c r="M20" t="n">
-        <v>1060.271045550332</v>
+        <v>544.2621276423173</v>
       </c>
       <c r="N20" t="n">
         <v>1096.663422488788</v>
       </c>
       <c r="O20" t="n">
-        <v>70.24786957409245</v>
+        <v>885.2478695740924</v>
       </c>
       <c r="P20" t="n">
-        <v>0.2870600406814136</v>
+        <v>633.038796227248</v>
       </c>
       <c r="Q20" t="n">
         <v>615.8520732695737</v>
@@ -9629,22 +9629,22 @@
         <v>716.8751175230994</v>
       </c>
       <c r="L23" t="n">
-        <v>536.481087937485</v>
+        <v>815</v>
       </c>
       <c r="M23" t="n">
-        <v>1060.271045550332</v>
+        <v>544.2621276423173</v>
       </c>
       <c r="N23" t="n">
         <v>1096.663422488788</v>
       </c>
       <c r="O23" t="n">
-        <v>70.24786957409245</v>
+        <v>750.7672643616811</v>
       </c>
       <c r="P23" t="n">
         <v>0.2870600406814136</v>
       </c>
       <c r="Q23" t="n">
-        <v>615.8520732695737</v>
+        <v>172.8226843274854</v>
       </c>
       <c r="R23" t="n">
         <v>294.54111633436</v>
@@ -9860,25 +9860,25 @@
         <v>120.6470157237802</v>
       </c>
       <c r="J26" t="n">
-        <v>430.3047365861567</v>
+        <v>35.04300624509033</v>
       </c>
       <c r="K26" t="n">
         <v>0</v>
       </c>
       <c r="L26" t="n">
-        <v>0</v>
+        <v>779</v>
       </c>
       <c r="M26" t="n">
         <v>1060.271045550332</v>
       </c>
       <c r="N26" t="n">
-        <v>1096.663422488788</v>
+        <v>477.2489580698352</v>
       </c>
       <c r="O26" t="n">
-        <v>849.2478695741181</v>
+        <v>637.7348152492415</v>
       </c>
       <c r="P26" t="n">
-        <v>332.0978109557855</v>
+        <v>779.2870600406815</v>
       </c>
       <c r="Q26" t="n">
         <v>615.8520732695737</v>
@@ -10100,22 +10100,22 @@
         <v>430.3047365861567</v>
       </c>
       <c r="K29" t="n">
-        <v>0</v>
+        <v>716.8751175230994</v>
       </c>
       <c r="L29" t="n">
         <v>0</v>
       </c>
       <c r="M29" t="n">
-        <v>1060.271045550332</v>
+        <v>675.2066789423629</v>
       </c>
       <c r="N29" t="n">
-        <v>649.4741734038525</v>
+        <v>1096.663422488788</v>
       </c>
       <c r="O29" t="n">
-        <v>849.2478695741249</v>
+        <v>849.2478695740924</v>
       </c>
       <c r="P29" t="n">
-        <v>779.287060040714</v>
+        <v>0.2870600406814136</v>
       </c>
       <c r="Q29" t="n">
         <v>615.8520732695737</v>
@@ -10340,22 +10340,22 @@
         <v>716.8751175230994</v>
       </c>
       <c r="L32" t="n">
-        <v>527.1775994334557</v>
+        <v>778.9999999999999</v>
       </c>
       <c r="M32" t="n">
-        <v>544.2621276423173</v>
+        <v>1060.271045550332</v>
       </c>
       <c r="N32" t="n">
-        <v>1096.663422488788</v>
+        <v>477.2489580698352</v>
       </c>
       <c r="O32" t="n">
-        <v>849.247869574139</v>
+        <v>22.40924805038325</v>
       </c>
       <c r="P32" t="n">
-        <v>0.2870600406814136</v>
+        <v>779.2870600406815</v>
       </c>
       <c r="Q32" t="n">
-        <v>615.8520732695737</v>
+        <v>515.273840737723</v>
       </c>
       <c r="R32" t="n">
         <v>294.54111633436</v>
@@ -10574,25 +10574,25 @@
         <v>430.3047365861567</v>
       </c>
       <c r="K35" t="n">
-        <v>0</v>
+        <v>716.8751175230994</v>
       </c>
       <c r="L35" t="n">
-        <v>0</v>
+        <v>463.1983439771709</v>
       </c>
       <c r="M35" t="n">
-        <v>1060.271045550332</v>
+        <v>544.2621276423173</v>
       </c>
       <c r="N35" t="n">
-        <v>1096.663422488788</v>
+        <v>429.4103365461411</v>
       </c>
       <c r="O35" t="n">
-        <v>403.0299382817363</v>
+        <v>849.2478695740924</v>
       </c>
       <c r="P35" t="n">
-        <v>779.2870600407517</v>
+        <v>779.2870600406815</v>
       </c>
       <c r="Q35" t="n">
-        <v>615.8520732695737</v>
+        <v>172.8226843274854</v>
       </c>
       <c r="R35" t="n">
         <v>294.54111633436</v>
@@ -10814,7 +10814,7 @@
         <v>716.8751175230994</v>
       </c>
       <c r="L38" t="n">
-        <v>751.3303335115488</v>
+        <v>779</v>
       </c>
       <c r="M38" t="n">
         <v>544.2621276423173</v>
@@ -10823,7 +10823,7 @@
         <v>477.2489580698352</v>
       </c>
       <c r="O38" t="n">
-        <v>849.2478695741845</v>
+        <v>821.5782030854823</v>
       </c>
       <c r="P38" t="n">
         <v>0.2870600406814136</v>
@@ -11048,22 +11048,22 @@
         <v>35.04300624509033</v>
       </c>
       <c r="K41" t="n">
-        <v>567.4869456748687</v>
+        <v>716.8751175230994</v>
       </c>
       <c r="L41" t="n">
-        <v>0</v>
+        <v>778.9999999999999</v>
       </c>
       <c r="M41" t="n">
-        <v>1060.271045550332</v>
+        <v>544.2621276423173</v>
       </c>
       <c r="N41" t="n">
-        <v>477.2489580698352</v>
+        <v>1096.663422488788</v>
       </c>
       <c r="O41" t="n">
-        <v>849.2478695742327</v>
+        <v>596.4541512152043</v>
       </c>
       <c r="P41" t="n">
-        <v>779.2870600408218</v>
+        <v>0.2870600406814136</v>
       </c>
       <c r="Q41" t="n">
         <v>615.8520732695737</v>
@@ -11282,25 +11282,25 @@
         <v>120.6470157237802</v>
       </c>
       <c r="J44" t="n">
-        <v>430.3047365861567</v>
+        <v>35.04300624509033</v>
       </c>
       <c r="K44" t="n">
-        <v>0</v>
+        <v>716.8751175230994</v>
       </c>
       <c r="L44" t="n">
-        <v>0</v>
+        <v>778.9999999999999</v>
       </c>
       <c r="M44" t="n">
         <v>1060.271045550332</v>
       </c>
       <c r="N44" t="n">
-        <v>1096.663422488788</v>
+        <v>770.8901751639733</v>
       </c>
       <c r="O44" t="n">
-        <v>845.088009431115</v>
+        <v>70.24786957409245</v>
       </c>
       <c r="P44" t="n">
-        <v>779.2870600408772</v>
+        <v>779.2870600406815</v>
       </c>
       <c r="Q44" t="n">
         <v>172.8226843274854</v>
@@ -23235,10 +23235,10 @@
         <v>0</v>
       </c>
       <c r="F11" t="n">
-        <v>179.8896287080119</v>
+        <v>0</v>
       </c>
       <c r="G11" t="n">
-        <v>178.7573722870162</v>
+        <v>0</v>
       </c>
       <c r="H11" t="n">
         <v>0</v>
@@ -23280,13 +23280,13 @@
         <v>0</v>
       </c>
       <c r="U11" t="n">
-        <v>0</v>
+        <v>424.2212965486107</v>
       </c>
       <c r="V11" t="n">
-        <v>0</v>
+        <v>71.32919911040022</v>
       </c>
       <c r="W11" t="n">
-        <v>136.9034946639831</v>
+        <v>0</v>
       </c>
       <c r="X11" t="n">
         <v>0</v>
@@ -23381,13 +23381,13 @@
         </is>
       </c>
       <c r="B13" t="n">
-        <v>62.11380033707866</v>
+        <v>0</v>
       </c>
       <c r="C13" t="n">
-        <v>47.72524664804467</v>
+        <v>0</v>
       </c>
       <c r="D13" t="n">
-        <v>60.53621805555548</v>
+        <v>0</v>
       </c>
       <c r="E13" t="n">
         <v>55.98090483695654</v>
@@ -23396,10 +23396,10 @@
         <v>49.38285596774193</v>
       </c>
       <c r="G13" t="n">
-        <v>20.04387284153003</v>
+        <v>0</v>
       </c>
       <c r="H13" t="n">
-        <v>0</v>
+        <v>3.77112610161862</v>
       </c>
       <c r="I13" t="n">
         <v>0</v>
@@ -23426,10 +23426,10 @@
         <v>462.4478973282775</v>
       </c>
       <c r="Q13" t="n">
-        <v>160.0624669370704</v>
+        <v>500.839266425598</v>
       </c>
       <c r="R13" t="n">
-        <v>501.6021279811511</v>
+        <v>346.100530434504</v>
       </c>
       <c r="S13" t="n">
         <v>137.3734797028554</v>
@@ -23444,7 +23444,7 @@
         <v>0</v>
       </c>
       <c r="W13" t="n">
-        <v>0</v>
+        <v>1.372809838709685</v>
       </c>
       <c r="X13" t="n">
         <v>22.44364543010755</v>
@@ -23648,25 +23648,25 @@
         <v>9.520773801143037</v>
       </c>
       <c r="L16" t="n">
-        <v>144.5476281577792</v>
+        <v>0</v>
       </c>
       <c r="M16" t="n">
         <v>241.6316114025499</v>
       </c>
       <c r="N16" t="n">
-        <v>292.1850752716849</v>
+        <v>11.93737172650322</v>
       </c>
       <c r="O16" t="n">
-        <v>361.445564079015</v>
+        <v>0</v>
       </c>
       <c r="P16" t="n">
-        <v>0</v>
+        <v>408.4478973282775</v>
       </c>
       <c r="Q16" t="n">
         <v>446.839266425598</v>
       </c>
       <c r="R16" t="n">
-        <v>69.80912952745274</v>
+        <v>447.6021279811511</v>
       </c>
       <c r="S16" t="n">
         <v>83.37347970285543</v>
@@ -23894,19 +23894,19 @@
         <v>292.1850752716849</v>
       </c>
       <c r="O19" t="n">
-        <v>361.445564079015</v>
+        <v>0</v>
       </c>
       <c r="P19" t="n">
-        <v>69.04626797189968</v>
+        <v>408.4478973282775</v>
       </c>
       <c r="Q19" t="n">
-        <v>0</v>
+        <v>446.839266425598</v>
       </c>
       <c r="R19" t="n">
-        <v>447.6021279811511</v>
+        <v>106.1802759810457</v>
       </c>
       <c r="S19" t="n">
-        <v>83.37347970285543</v>
+        <v>0</v>
       </c>
       <c r="T19" t="n">
         <v>0</v>
@@ -24092,13 +24092,13 @@
         </is>
       </c>
       <c r="B22" t="n">
-        <v>8.113800337078658</v>
+        <v>0</v>
       </c>
       <c r="C22" t="n">
         <v>0</v>
       </c>
       <c r="D22" t="n">
-        <v>6.53621805555548</v>
+        <v>0</v>
       </c>
       <c r="E22" t="n">
         <v>1.98090483695654</v>
@@ -24131,19 +24131,19 @@
         <v>292.1850752716849</v>
       </c>
       <c r="O22" t="n">
-        <v>0</v>
+        <v>361.445564079015</v>
       </c>
       <c r="P22" t="n">
-        <v>408.4478973282775</v>
+        <v>0</v>
       </c>
       <c r="Q22" t="n">
         <v>446.839266425598</v>
       </c>
       <c r="R22" t="n">
-        <v>22.80679627819018</v>
+        <v>167.8326276229424</v>
       </c>
       <c r="S22" t="n">
-        <v>83.37347970285543</v>
+        <v>0</v>
       </c>
       <c r="T22" t="n">
         <v>0</v>
@@ -24335,7 +24335,7 @@
         <v>0</v>
       </c>
       <c r="D25" t="n">
-        <v>6.53621805555548</v>
+        <v>0</v>
       </c>
       <c r="E25" t="n">
         <v>1.98090483695654</v>
@@ -24359,10 +24359,10 @@
         <v>9.520773801143037</v>
       </c>
       <c r="L25" t="n">
-        <v>144.5476281577792</v>
+        <v>54.07668981505995</v>
       </c>
       <c r="M25" t="n">
-        <v>241.6316114025499</v>
+        <v>0</v>
       </c>
       <c r="N25" t="n">
         <v>292.1850752716849</v>
@@ -24374,7 +24374,7 @@
         <v>408.4478973282775</v>
       </c>
       <c r="Q25" t="n">
-        <v>108.2004986247733</v>
+        <v>446.839266425598</v>
       </c>
       <c r="R25" t="n">
         <v>0</v>
@@ -24417,13 +24417,13 @@
         <v>0</v>
       </c>
       <c r="E26" t="n">
-        <v>179.3632896068686</v>
+        <v>0</v>
       </c>
       <c r="F26" t="n">
-        <v>135.7952490003845</v>
+        <v>179.8896287080119</v>
       </c>
       <c r="G26" t="n">
-        <v>178.7573722870162</v>
+        <v>0</v>
       </c>
       <c r="H26" t="n">
         <v>0</v>
@@ -24465,16 +24465,16 @@
         <v>0</v>
       </c>
       <c r="U26" t="n">
-        <v>424.2212965486107</v>
+        <v>0</v>
       </c>
       <c r="V26" t="n">
-        <v>0</v>
+        <v>404.8510241668239</v>
       </c>
       <c r="W26" t="n">
         <v>0</v>
       </c>
       <c r="X26" t="n">
-        <v>0</v>
+        <v>333.3965545680443</v>
       </c>
       <c r="Y26" t="n">
         <v>0</v>
@@ -24566,7 +24566,7 @@
         </is>
       </c>
       <c r="B28" t="n">
-        <v>62.11380033707866</v>
+        <v>0</v>
       </c>
       <c r="C28" t="n">
         <v>47.72524664804467</v>
@@ -24578,7 +24578,7 @@
         <v>55.98090483695654</v>
       </c>
       <c r="F28" t="n">
-        <v>49.38285596774193</v>
+        <v>2.706500370232149</v>
       </c>
       <c r="G28" t="n">
         <v>20.04387284153003</v>
@@ -24614,7 +24614,7 @@
         <v>500.839266425598</v>
       </c>
       <c r="R28" t="n">
-        <v>160.8253284926234</v>
+        <v>268.2426745885022</v>
       </c>
       <c r="S28" t="n">
         <v>137.3734797028554</v>
@@ -24629,7 +24629,7 @@
         <v>0</v>
       </c>
       <c r="W28" t="n">
-        <v>0</v>
+        <v>1.372809838709685</v>
       </c>
       <c r="X28" t="n">
         <v>22.44364543010755</v>
@@ -24654,16 +24654,16 @@
         <v>0</v>
       </c>
       <c r="E29" t="n">
-        <v>153.3632896068686</v>
+        <v>0</v>
       </c>
       <c r="F29" t="n">
-        <v>153.8896287080119</v>
+        <v>0</v>
       </c>
       <c r="G29" t="n">
-        <v>152.7573722870162</v>
+        <v>0</v>
       </c>
       <c r="H29" t="n">
-        <v>68.24831801268876</v>
+        <v>157.0096587035274</v>
       </c>
       <c r="I29" t="n">
         <v>0</v>
@@ -24702,7 +24702,7 @@
         <v>0</v>
       </c>
       <c r="U29" t="n">
-        <v>0</v>
+        <v>371.248949911058</v>
       </c>
       <c r="V29" t="n">
         <v>0</v>
@@ -24842,16 +24842,16 @@
         <v>320.1850752716849</v>
       </c>
       <c r="O31" t="n">
-        <v>0</v>
+        <v>389.445564079015</v>
       </c>
       <c r="P31" t="n">
-        <v>297.3129142515843</v>
+        <v>383.4694781537204</v>
       </c>
       <c r="Q31" t="n">
         <v>474.839266425598</v>
       </c>
       <c r="R31" t="n">
-        <v>475.6021279811511</v>
+        <v>0</v>
       </c>
       <c r="S31" t="n">
         <v>111.3734797028554</v>
@@ -24933,7 +24933,7 @@
         <v>0</v>
       </c>
       <c r="S32" t="n">
-        <v>10.25860861458523</v>
+        <v>0</v>
       </c>
       <c r="T32" t="n">
         <v>0</v>
@@ -24951,7 +24951,7 @@
         <v>0</v>
       </c>
       <c r="Y32" t="n">
-        <v>0</v>
+        <v>10.25860861458563</v>
       </c>
     </row>
     <row r="33">
@@ -25070,13 +25070,13 @@
         <v>0.5207738011430365</v>
       </c>
       <c r="L34" t="n">
-        <v>135.5476281577792</v>
+        <v>0</v>
       </c>
       <c r="M34" t="n">
         <v>232.6316114025499</v>
       </c>
       <c r="N34" t="n">
-        <v>283.1850752716849</v>
+        <v>276.6686292398607</v>
       </c>
       <c r="O34" t="n">
         <v>0</v>
@@ -25085,7 +25085,7 @@
         <v>0</v>
       </c>
       <c r="Q34" t="n">
-        <v>295.7751922359946</v>
+        <v>437.839266425598</v>
       </c>
       <c r="R34" t="n">
         <v>438.6021279811511</v>
@@ -25137,7 +25137,7 @@
         <v>0</v>
       </c>
       <c r="H35" t="n">
-        <v>10.2586086143001</v>
+        <v>0</v>
       </c>
       <c r="I35" t="n">
         <v>0</v>
@@ -25176,7 +25176,7 @@
         <v>0</v>
       </c>
       <c r="U35" t="n">
-        <v>0</v>
+        <v>10.25860861458591</v>
       </c>
       <c r="V35" t="n">
         <v>0</v>
@@ -25310,7 +25310,7 @@
         <v>0</v>
       </c>
       <c r="M37" t="n">
-        <v>0</v>
+        <v>232.6316114025499</v>
       </c>
       <c r="N37" t="n">
         <v>283.1850752716849</v>
@@ -25322,7 +25322,7 @@
         <v>399.4478973282775</v>
       </c>
       <c r="Q37" t="n">
-        <v>425.0365780730378</v>
+        <v>192.4049666704879</v>
       </c>
       <c r="R37" t="n">
         <v>0</v>
@@ -25425,7 +25425,7 @@
         <v>0</v>
       </c>
       <c r="Y38" t="n">
-        <v>10.25860861421376</v>
+        <v>10.25860861458563</v>
       </c>
     </row>
     <row r="39">
@@ -25544,7 +25544,7 @@
         <v>0.5207738011430365</v>
       </c>
       <c r="L40" t="n">
-        <v>135.5476281577792</v>
+        <v>0</v>
       </c>
       <c r="M40" t="n">
         <v>232.6316114025499</v>
@@ -25553,19 +25553,19 @@
         <v>283.1850752716849</v>
       </c>
       <c r="O40" t="n">
-        <v>295.7751922359946</v>
+        <v>352.445564079015</v>
       </c>
       <c r="P40" t="n">
-        <v>0</v>
+        <v>399.4478973282775</v>
       </c>
       <c r="Q40" t="n">
-        <v>0</v>
+        <v>192.4049666704879</v>
       </c>
       <c r="R40" t="n">
-        <v>438.6021279811511</v>
+        <v>0</v>
       </c>
       <c r="S40" t="n">
-        <v>74.37347970285543</v>
+        <v>0</v>
       </c>
       <c r="T40" t="n">
         <v>0</v>
@@ -25593,19 +25593,19 @@
         </is>
       </c>
       <c r="B41" t="n">
-        <v>0</v>
+        <v>286.9993129555745</v>
       </c>
       <c r="C41" t="n">
         <v>254.4745782429939</v>
       </c>
       <c r="D41" t="n">
-        <v>215.3391557398498</v>
+        <v>0</v>
       </c>
       <c r="E41" t="n">
         <v>209.3632896068686</v>
       </c>
       <c r="F41" t="n">
-        <v>209.8896287080119</v>
+        <v>11.26082088975875</v>
       </c>
       <c r="G41" t="n">
         <v>208.7573722870162</v>
@@ -25644,7 +25644,7 @@
         <v>0</v>
       </c>
       <c r="S41" t="n">
-        <v>270.3131828581394</v>
+        <v>0</v>
       </c>
       <c r="T41" t="n">
         <v>0</v>
@@ -25659,7 +25659,7 @@
         <v>0</v>
       </c>
       <c r="X41" t="n">
-        <v>0</v>
+        <v>397.2818334606677</v>
       </c>
       <c r="Y41" t="n">
         <v>0</v>
@@ -25723,7 +25723,7 @@
         <v>352.2737972923793</v>
       </c>
       <c r="S42" t="n">
-        <v>53.96794860432524</v>
+        <v>271.5639999646113</v>
       </c>
       <c r="T42" t="n">
         <v>0</v>
@@ -25735,7 +25735,7 @@
         <v>0</v>
       </c>
       <c r="W42" t="n">
-        <v>237.3731429098285</v>
+        <v>0.6613597939094689</v>
       </c>
       <c r="X42" t="n">
         <v>0</v>
@@ -25769,7 +25769,7 @@
         <v>50.04387284153003</v>
       </c>
       <c r="H43" t="n">
-        <v>0</v>
+        <v>33.77112610161862</v>
       </c>
       <c r="I43" t="n">
         <v>0</v>
@@ -25830,28 +25830,28 @@
         </is>
       </c>
       <c r="B44" t="n">
-        <v>366.9993129555745</v>
+        <v>0</v>
       </c>
       <c r="C44" t="n">
-        <v>334.4745782429939</v>
+        <v>106.6302885399382</v>
       </c>
       <c r="D44" t="n">
-        <v>295.3391557398498</v>
+        <v>0</v>
       </c>
       <c r="E44" t="n">
         <v>0</v>
       </c>
       <c r="F44" t="n">
-        <v>0</v>
+        <v>289.8896287080119</v>
       </c>
       <c r="G44" t="n">
         <v>288.7573722870162</v>
       </c>
       <c r="H44" t="n">
-        <v>293.0096587035274</v>
+        <v>0</v>
       </c>
       <c r="I44" t="n">
-        <v>35.08115968268461</v>
+        <v>0</v>
       </c>
       <c r="J44" t="n">
         <v>0</v>
@@ -25887,7 +25887,7 @@
         <v>471.6755817285639</v>
       </c>
       <c r="U44" t="n">
-        <v>2.154781154736497</v>
+        <v>534.2212965486107</v>
       </c>
       <c r="V44" t="n">
         <v>0</v>
@@ -25899,7 +25899,7 @@
         <v>0</v>
       </c>
       <c r="Y44" t="n">
-        <v>0</v>
+        <v>396.3174326828064</v>
       </c>
     </row>
     <row r="45">
@@ -25909,19 +25909,19 @@
         </is>
       </c>
       <c r="B45" t="n">
-        <v>269.5565566463266</v>
+        <v>0</v>
       </c>
       <c r="C45" t="n">
-        <v>246.0999124455193</v>
+        <v>0</v>
       </c>
       <c r="D45" t="n">
-        <v>232.9376868977026</v>
+        <v>0</v>
       </c>
       <c r="E45" t="n">
-        <v>227.6720972219126</v>
+        <v>0</v>
       </c>
       <c r="F45" t="n">
-        <v>224.6362423378769</v>
+        <v>0</v>
       </c>
       <c r="G45" t="n">
         <v>210.7395358750273</v>
@@ -25930,7 +25930,7 @@
         <v>217.1680871864211</v>
       </c>
       <c r="I45" t="n">
-        <v>102.1263858913485</v>
+        <v>0</v>
       </c>
       <c r="J45" t="n">
         <v>0</v>
@@ -25954,25 +25954,25 @@
         <v>0</v>
       </c>
       <c r="Q45" t="n">
-        <v>0</v>
+        <v>58.07926509047959</v>
       </c>
       <c r="R45" t="n">
-        <v>0</v>
+        <v>432.2737972923793</v>
       </c>
       <c r="S45" t="n">
-        <v>351.5639999646113</v>
+        <v>196.7275907235714</v>
       </c>
       <c r="T45" t="n">
-        <v>0</v>
+        <v>290.3577652175138</v>
       </c>
       <c r="U45" t="n">
-        <v>0</v>
+        <v>285.2103597601867</v>
       </c>
       <c r="V45" t="n">
-        <v>0</v>
+        <v>299.5106671915202</v>
       </c>
       <c r="W45" t="n">
-        <v>180.7070256975813</v>
+        <v>317.3731429098285</v>
       </c>
       <c r="X45" t="n">
         <v>0</v>
@@ -26042,7 +26042,7 @@
         <v>247.3734797028554</v>
       </c>
       <c r="T46" t="n">
-        <v>95.02456650625771</v>
+        <v>16.8801632603309</v>
       </c>
       <c r="U46" t="n">
         <v>35.95839127445794</v>
@@ -26110,7 +26110,7 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>3791612.675886257</v>
+        <v>3791612.675886258</v>
       </c>
     </row>
     <row r="6">
@@ -26126,7 +26126,7 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>5620398.07942505</v>
+        <v>5620398.079425052</v>
       </c>
     </row>
     <row r="8">
@@ -26134,7 +26134,7 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>6534790.781194444</v>
+        <v>6534790.781194445</v>
       </c>
     </row>
     <row r="9">
@@ -26150,7 +26150,7 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>8283043.329448724</v>
+        <v>8283043.329448726</v>
       </c>
     </row>
     <row r="11">
@@ -26158,7 +26158,7 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>9153897.160161469</v>
+        <v>9153897.160161471</v>
       </c>
     </row>
     <row r="12">
@@ -26174,7 +26174,7 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>10989172.34710555</v>
+        <v>10989172.34710553</v>
       </c>
     </row>
     <row r="14">
@@ -26182,7 +26182,7 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>11906801.24242678</v>
+        <v>11906801.24242674</v>
       </c>
     </row>
     <row r="15">
@@ -26190,7 +26190,7 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>12680550.74584608</v>
+        <v>12680550.74584605</v>
       </c>
     </row>
     <row r="16">
@@ -26198,7 +26198,7 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>13286521.85617682</v>
+        <v>13286521.85617678</v>
       </c>
     </row>
   </sheetData>
@@ -26281,31 +26281,31 @@
         <v>1126337.93458107</v>
       </c>
       <c r="F2" t="n">
+        <v>1219190.269025865</v>
+      </c>
+      <c r="G2" t="n">
+        <v>1219190.269025865</v>
+      </c>
+      <c r="H2" t="n">
         <v>1219190.269025864</v>
       </c>
-      <c r="G2" t="n">
+      <c r="I2" t="n">
         <v>1219190.269025864</v>
-      </c>
-      <c r="H2" t="n">
-        <v>1219190.269025865</v>
-      </c>
-      <c r="I2" t="n">
-        <v>1219190.269025865</v>
       </c>
       <c r="J2" t="n">
         <v>1115217.11410107</v>
       </c>
       <c r="K2" t="n">
-        <v>1161138.440950334</v>
+        <v>1161138.440950333</v>
       </c>
       <c r="L2" t="n">
         <v>1223505.193761599</v>
       </c>
       <c r="M2" t="n">
-        <v>1223505.193761621</v>
+        <v>1223505.193761598</v>
       </c>
       <c r="N2" t="n">
-        <v>1223505.193761628</v>
+        <v>1223505.193761598</v>
       </c>
       <c r="O2" t="n">
         <v>1031689.199627948</v>
@@ -26373,49 +26373,49 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>556518.3877202003</v>
+        <v>551678.2037907121</v>
       </c>
       <c r="C4" t="n">
-        <v>554765.5452197595</v>
+        <v>549925.3612902712</v>
       </c>
       <c r="D4" t="n">
-        <v>553010.324879062</v>
+        <v>548170.1409495736</v>
       </c>
       <c r="E4" t="n">
-        <v>474768.9161162032</v>
+        <v>469977.895301786</v>
       </c>
       <c r="F4" t="n">
-        <v>525348.7383112749</v>
+        <v>520557.7174968577</v>
       </c>
       <c r="G4" t="n">
-        <v>523678.7566207297</v>
+        <v>518887.7358063125</v>
       </c>
       <c r="H4" t="n">
-        <v>522006.457090894</v>
+        <v>517215.4362764768</v>
       </c>
       <c r="I4" t="n">
-        <v>520331.8230037717</v>
+        <v>515540.8021893547</v>
       </c>
       <c r="J4" t="n">
-        <v>464813.3679854202</v>
+        <v>460130.3405348168</v>
       </c>
       <c r="K4" t="n">
-        <v>488548.683349176</v>
+        <v>483865.6558985728</v>
       </c>
       <c r="L4" t="n">
-        <v>521101.9613805412</v>
+        <v>516418.1980532588</v>
       </c>
       <c r="M4" t="n">
-        <v>519382.0000515418</v>
+        <v>514698.2367242419</v>
       </c>
       <c r="N4" t="n">
-        <v>517659.5657041433</v>
+        <v>512975.8023768382</v>
       </c>
       <c r="O4" t="n">
-        <v>411958.788736175</v>
+        <v>407275.7612855717</v>
       </c>
       <c r="P4" t="n">
-        <v>289436.0308461937</v>
+        <v>284753.0033955905</v>
       </c>
     </row>
     <row r="5">
@@ -26477,49 +26477,49 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>332799.0526123948</v>
+        <v>337639.2365418829</v>
       </c>
       <c r="C6" t="n">
-        <v>621431.8951128357</v>
+        <v>626272.0790423237</v>
       </c>
       <c r="D6" t="n">
-        <v>623187.1154535334</v>
+        <v>628027.2993830213</v>
       </c>
       <c r="E6" t="n">
-        <v>403101.4934648663</v>
+        <v>407892.5142792839</v>
       </c>
       <c r="F6" t="n">
-        <v>577634.2797145889</v>
+        <v>582425.300529007</v>
       </c>
       <c r="G6" t="n">
-        <v>622504.2614051346</v>
+        <v>627295.282219552</v>
       </c>
       <c r="H6" t="n">
-        <v>624176.5609349705</v>
+        <v>628967.5817493874</v>
       </c>
       <c r="I6" t="n">
-        <v>625851.1950220928</v>
+        <v>630642.2158365094</v>
       </c>
       <c r="J6" t="n">
-        <v>173117.02111565</v>
+        <v>177800.0485662531</v>
       </c>
       <c r="K6" t="n">
-        <v>540125.2386011577</v>
+        <v>544808.2660517604</v>
       </c>
       <c r="L6" t="n">
-        <v>601228.1603810575</v>
+        <v>605911.9237083398</v>
       </c>
       <c r="M6" t="n">
-        <v>632548.121710079</v>
+        <v>637231.8850373562</v>
       </c>
       <c r="N6" t="n">
-        <v>634270.5560574842</v>
+        <v>638954.3193847599</v>
       </c>
       <c r="O6" t="n">
-        <v>493573.7558917734</v>
+        <v>498256.7833423765</v>
       </c>
       <c r="P6" t="n">
-        <v>461494.3145947813</v>
+        <v>466177.3420453845</v>
       </c>
     </row>
   </sheetData>
@@ -26987,13 +26987,13 @@
         <v>54</v>
       </c>
       <c r="G2" t="n">
+        <v>0</v>
+      </c>
+      <c r="H2" t="n">
         <v>-0</v>
       </c>
-      <c r="H2" t="n">
-        <v>0</v>
-      </c>
       <c r="I2" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="J2" t="n">
         <v>171</v>
@@ -27005,10 +27005,10 @@
         <v>37</v>
       </c>
       <c r="M2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="N2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="O2" t="n">
         <v>78</v>
@@ -27024,7 +27024,7 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="C3" t="n">
         <v>-0</v>
@@ -27433,7 +27433,7 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>0</v>
+        <v>400</v>
       </c>
       <c r="C2" t="n">
         <v>400</v>
@@ -27451,52 +27451,52 @@
         <v>400</v>
       </c>
       <c r="H2" t="n">
+        <v>0</v>
+      </c>
+      <c r="I2" t="n">
+        <v>0</v>
+      </c>
+      <c r="J2" t="n">
+        <v>0</v>
+      </c>
+      <c r="K2" t="n">
+        <v>0</v>
+      </c>
+      <c r="L2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M2" t="n">
+        <v>0</v>
+      </c>
+      <c r="N2" t="n">
+        <v>0</v>
+      </c>
+      <c r="O2" t="n">
+        <v>0</v>
+      </c>
+      <c r="P2" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q2" t="n">
+        <v>0</v>
+      </c>
+      <c r="R2" t="n">
+        <v>0</v>
+      </c>
+      <c r="S2" t="n">
+        <v>0</v>
+      </c>
+      <c r="T2" t="n">
         <v>400</v>
-      </c>
-      <c r="I2" t="n">
-        <v>52.63096829726986</v>
-      </c>
-      <c r="J2" t="n">
-        <v>0</v>
-      </c>
-      <c r="K2" t="n">
-        <v>0</v>
-      </c>
-      <c r="L2" t="n">
-        <v>0</v>
-      </c>
-      <c r="M2" t="n">
-        <v>0</v>
-      </c>
-      <c r="N2" t="n">
-        <v>0</v>
-      </c>
-      <c r="O2" t="n">
-        <v>0</v>
-      </c>
-      <c r="P2" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q2" t="n">
-        <v>0</v>
-      </c>
-      <c r="R2" t="n">
-        <v>250.8785988282945</v>
-      </c>
-      <c r="S2" t="n">
-        <v>400</v>
-      </c>
-      <c r="T2" t="n">
-        <v>0</v>
       </c>
       <c r="U2" t="n">
         <v>400</v>
       </c>
       <c r="V2" t="n">
-        <v>0</v>
+        <v>400</v>
       </c>
       <c r="W2" t="n">
-        <v>400</v>
+        <v>303.5095671255646</v>
       </c>
       <c r="X2" t="n">
         <v>400</v>
@@ -27512,19 +27512,19 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>99.91019735338352</v>
+        <v>384.5565566463266</v>
       </c>
       <c r="C3" t="n">
         <v>361.0999124455193</v>
       </c>
       <c r="D3" t="n">
-        <v>347.9376868977026</v>
+        <v>0</v>
       </c>
       <c r="E3" t="n">
-        <v>342.6720972219126</v>
+        <v>0</v>
       </c>
       <c r="F3" t="n">
-        <v>339.6362423378769</v>
+        <v>172.5204020740698</v>
       </c>
       <c r="G3" t="n">
         <v>325.7395358750273</v>
@@ -27557,7 +27557,7 @@
         <v>0</v>
       </c>
       <c r="Q3" t="n">
-        <v>0</v>
+        <v>173.0792650904796</v>
       </c>
       <c r="R3" t="n">
         <v>400</v>
@@ -27569,7 +27569,7 @@
         <v>400</v>
       </c>
       <c r="U3" t="n">
-        <v>0</v>
+        <v>400</v>
       </c>
       <c r="V3" t="n">
         <v>400</v>
@@ -27606,13 +27606,13 @@
         <v>400</v>
       </c>
       <c r="G4" t="n">
-        <v>400</v>
+        <v>245.04387284153</v>
       </c>
       <c r="H4" t="n">
         <v>400</v>
       </c>
       <c r="I4" t="n">
-        <v>400</v>
+        <v>176.6334556201183</v>
       </c>
       <c r="J4" t="n">
         <v>400</v>
@@ -27642,13 +27642,13 @@
         <v>400</v>
       </c>
       <c r="S4" t="n">
+        <v>362.3734797028554</v>
+      </c>
+      <c r="T4" t="n">
         <v>400</v>
       </c>
-      <c r="T4" t="n">
-        <v>254.4407163526612</v>
-      </c>
       <c r="U4" t="n">
-        <v>150.9583912744579</v>
+        <v>308.8136523120777</v>
       </c>
       <c r="V4" t="n">
         <v>199.1703102162162</v>
@@ -27660,7 +27660,7 @@
         <v>247.4436454301076</v>
       </c>
       <c r="Y4" t="n">
-        <v>287.4653528494624</v>
+        <v>400</v>
       </c>
     </row>
     <row r="5">
@@ -27682,55 +27682,55 @@
         <v>400</v>
       </c>
       <c r="F5" t="n">
+        <v>0</v>
+      </c>
+      <c r="G5" t="n">
+        <v>153.4284074428801</v>
+      </c>
+      <c r="H5" t="n">
+        <v>0</v>
+      </c>
+      <c r="I5" t="n">
+        <v>150.0811596826846</v>
+      </c>
+      <c r="J5" t="n">
+        <v>0</v>
+      </c>
+      <c r="K5" t="n">
+        <v>0</v>
+      </c>
+      <c r="L5" t="n">
+        <v>0</v>
+      </c>
+      <c r="M5" t="n">
+        <v>0</v>
+      </c>
+      <c r="N5" t="n">
+        <v>0</v>
+      </c>
+      <c r="O5" t="n">
+        <v>0</v>
+      </c>
+      <c r="P5" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q5" t="n">
+        <v>0</v>
+      </c>
+      <c r="R5" t="n">
+        <v>0</v>
+      </c>
+      <c r="S5" t="n">
+        <v>0</v>
+      </c>
+      <c r="T5" t="n">
         <v>400</v>
-      </c>
-      <c r="G5" t="n">
-        <v>0</v>
-      </c>
-      <c r="H5" t="n">
-        <v>400</v>
-      </c>
-      <c r="I5" t="n">
-        <v>0</v>
-      </c>
-      <c r="J5" t="n">
-        <v>0</v>
-      </c>
-      <c r="K5" t="n">
-        <v>0</v>
-      </c>
-      <c r="L5" t="n">
-        <v>0</v>
-      </c>
-      <c r="M5" t="n">
-        <v>0</v>
-      </c>
-      <c r="N5" t="n">
-        <v>0</v>
-      </c>
-      <c r="O5" t="n">
-        <v>0</v>
-      </c>
-      <c r="P5" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q5" t="n">
-        <v>0</v>
-      </c>
-      <c r="R5" t="n">
-        <v>250.8785988282945</v>
-      </c>
-      <c r="S5" t="n">
-        <v>0</v>
-      </c>
-      <c r="T5" t="n">
-        <v>52.63096829726976</v>
       </c>
       <c r="U5" t="n">
         <v>400</v>
       </c>
       <c r="V5" t="n">
-        <v>0</v>
+        <v>400</v>
       </c>
       <c r="W5" t="n">
         <v>400</v>
@@ -27752,13 +27752,13 @@
         <v>384.5565566463266</v>
       </c>
       <c r="C6" t="n">
-        <v>361.0999124455193</v>
+        <v>251.3119749597992</v>
       </c>
       <c r="D6" t="n">
-        <v>5.963424826672224</v>
+        <v>0</v>
       </c>
       <c r="E6" t="n">
-        <v>0</v>
+        <v>342.6720972219126</v>
       </c>
       <c r="F6" t="n">
         <v>339.6362423378769</v>
@@ -27794,7 +27794,7 @@
         <v>0</v>
       </c>
       <c r="Q6" t="n">
-        <v>0</v>
+        <v>173.0792650904796</v>
       </c>
       <c r="R6" t="n">
         <v>400</v>
@@ -27806,7 +27806,7 @@
         <v>400</v>
       </c>
       <c r="U6" t="n">
-        <v>400</v>
+        <v>0</v>
       </c>
       <c r="V6" t="n">
         <v>400</v>
@@ -27828,22 +27828,22 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>287.1138003370787</v>
+        <v>400</v>
       </c>
       <c r="C7" t="n">
         <v>272.7252466480447</v>
       </c>
       <c r="D7" t="n">
-        <v>400</v>
+        <v>285.5362180555555</v>
       </c>
       <c r="E7" t="n">
         <v>400</v>
       </c>
       <c r="F7" t="n">
-        <v>400</v>
+        <v>274.3828559677419</v>
       </c>
       <c r="G7" t="n">
-        <v>400</v>
+        <v>355.9574538756183</v>
       </c>
       <c r="H7" t="n">
         <v>400</v>
@@ -27882,22 +27882,22 @@
         <v>400</v>
       </c>
       <c r="T7" t="n">
+        <v>210.0245665062577</v>
+      </c>
+      <c r="U7" t="n">
+        <v>150.9583912744579</v>
+      </c>
+      <c r="V7" t="n">
         <v>400</v>
       </c>
-      <c r="U7" t="n">
+      <c r="W7" t="n">
         <v>400</v>
       </c>
-      <c r="V7" t="n">
-        <v>228.4638772242731</v>
-      </c>
-      <c r="W7" t="n">
-        <v>226.3728098387097</v>
-      </c>
       <c r="X7" t="n">
-        <v>247.4436454301076</v>
+        <v>400</v>
       </c>
       <c r="Y7" t="n">
-        <v>287.4653528494624</v>
+        <v>400</v>
       </c>
     </row>
     <row r="8">
@@ -27913,22 +27913,22 @@
         <v>0</v>
       </c>
       <c r="D8" t="n">
-        <v>0</v>
+        <v>400</v>
       </c>
       <c r="E8" t="n">
         <v>400</v>
       </c>
       <c r="F8" t="n">
-        <v>400</v>
+        <v>0</v>
       </c>
       <c r="G8" t="n">
-        <v>153.4284074428802</v>
+        <v>52.63096829727004</v>
       </c>
       <c r="H8" t="n">
         <v>0</v>
       </c>
       <c r="I8" t="n">
-        <v>150.0811596826846</v>
+        <v>0</v>
       </c>
       <c r="J8" t="n">
         <v>0</v>
@@ -27955,7 +27955,7 @@
         <v>0</v>
       </c>
       <c r="R8" t="n">
-        <v>0</v>
+        <v>250.8785988282945</v>
       </c>
       <c r="S8" t="n">
         <v>400</v>
@@ -27992,7 +27992,7 @@
         <v>361.0999124455193</v>
       </c>
       <c r="D9" t="n">
-        <v>347.9376868977026</v>
+        <v>229.8483048521569</v>
       </c>
       <c r="E9" t="n">
         <v>342.6720972219126</v>
@@ -28007,7 +28007,7 @@
         <v>332.1680871864211</v>
       </c>
       <c r="I9" t="n">
-        <v>99.03700384580273</v>
+        <v>217.1263858913485</v>
       </c>
       <c r="J9" t="n">
         <v>0</v>
@@ -28034,7 +28034,7 @@
         <v>173.0792650904796</v>
       </c>
       <c r="R9" t="n">
-        <v>0</v>
+        <v>400</v>
       </c>
       <c r="S9" t="n">
         <v>400</v>
@@ -28049,7 +28049,7 @@
         <v>400</v>
       </c>
       <c r="W9" t="n">
-        <v>400</v>
+        <v>0</v>
       </c>
       <c r="X9" t="n">
         <v>400</v>
@@ -28065,31 +28065,31 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>400</v>
+        <v>287.1138003370787</v>
       </c>
       <c r="C10" t="n">
         <v>400</v>
       </c>
       <c r="D10" t="n">
+        <v>353.5680591050792</v>
+      </c>
+      <c r="E10" t="n">
+        <v>280.9809048369565</v>
+      </c>
+      <c r="F10" t="n">
+        <v>274.3828559677419</v>
+      </c>
+      <c r="G10" t="n">
+        <v>245.04387284153</v>
+      </c>
+      <c r="H10" t="n">
+        <v>228.7711261016186</v>
+      </c>
+      <c r="I10" t="n">
+        <v>176.6334556201183</v>
+      </c>
+      <c r="J10" t="n">
         <v>400</v>
-      </c>
-      <c r="E10" t="n">
-        <v>400</v>
-      </c>
-      <c r="F10" t="n">
-        <v>400</v>
-      </c>
-      <c r="G10" t="n">
-        <v>400</v>
-      </c>
-      <c r="H10" t="n">
-        <v>400</v>
-      </c>
-      <c r="I10" t="n">
-        <v>400</v>
-      </c>
-      <c r="J10" t="n">
-        <v>35.26894883590776</v>
       </c>
       <c r="K10" t="n">
         <v>288.520773801143</v>
@@ -28122,19 +28122,19 @@
         <v>400</v>
       </c>
       <c r="U10" t="n">
-        <v>225.7037133386441</v>
+        <v>400</v>
       </c>
       <c r="V10" t="n">
-        <v>199.1703102162162</v>
+        <v>400</v>
       </c>
       <c r="W10" t="n">
-        <v>226.3728098387097</v>
+        <v>400</v>
       </c>
       <c r="X10" t="n">
-        <v>247.4436454301076</v>
+        <v>400</v>
       </c>
       <c r="Y10" t="n">
-        <v>400</v>
+        <v>287.4653528494624</v>
       </c>
     </row>
     <row r="11">
@@ -28262,10 +28262,10 @@
         <v>225</v>
       </c>
       <c r="O12" t="n">
+        <v>19.11687125883921</v>
+      </c>
+      <c r="P12" t="n">
         <v>225</v>
-      </c>
-      <c r="P12" t="n">
-        <v>19.11687125883908</v>
       </c>
       <c r="Q12" t="n">
         <v>225</v>
@@ -28399,7 +28399,7 @@
         <v>279</v>
       </c>
       <c r="H14" t="n">
-        <v>275.549808614586</v>
+        <v>279</v>
       </c>
       <c r="I14" t="n">
         <v>150.0811596826846</v>
@@ -28444,7 +28444,7 @@
         <v>279</v>
       </c>
       <c r="W14" t="n">
-        <v>279</v>
+        <v>275.5498086145859</v>
       </c>
       <c r="X14" t="n">
         <v>279</v>
@@ -28481,22 +28481,22 @@
         <v>279</v>
       </c>
       <c r="I15" t="n">
+        <v>217.1263858913485</v>
+      </c>
+      <c r="J15" t="n">
+        <v>0</v>
+      </c>
+      <c r="K15" t="n">
         <v>279</v>
       </c>
-      <c r="J15" t="n">
-        <v>155.670590267103</v>
-      </c>
-      <c r="K15" t="n">
-        <v>0</v>
-      </c>
       <c r="L15" t="n">
         <v>0</v>
       </c>
       <c r="M15" t="n">
-        <v>0</v>
+        <v>279</v>
       </c>
       <c r="N15" t="n">
-        <v>279</v>
+        <v>44.46493928527497</v>
       </c>
       <c r="O15" t="n">
         <v>0</v>
@@ -28505,7 +28505,7 @@
         <v>0</v>
       </c>
       <c r="Q15" t="n">
-        <v>279</v>
+        <v>173.0792650904796</v>
       </c>
       <c r="R15" t="n">
         <v>279</v>
@@ -28666,10 +28666,10 @@
         <v>0</v>
       </c>
       <c r="R17" t="n">
-        <v>250.8785988282945</v>
+        <v>247.42840744288</v>
       </c>
       <c r="S17" t="n">
-        <v>275.5498086145856</v>
+        <v>279</v>
       </c>
       <c r="T17" t="n">
         <v>279</v>
@@ -28718,13 +28718,13 @@
         <v>279</v>
       </c>
       <c r="I18" t="n">
-        <v>279</v>
+        <v>217.1263858913485</v>
       </c>
       <c r="J18" t="n">
         <v>279</v>
       </c>
       <c r="K18" t="n">
-        <v>155.670590267103</v>
+        <v>0</v>
       </c>
       <c r="L18" t="n">
         <v>0</v>
@@ -28736,13 +28736,13 @@
         <v>0</v>
       </c>
       <c r="O18" t="n">
-        <v>0</v>
+        <v>279</v>
       </c>
       <c r="P18" t="n">
-        <v>0</v>
+        <v>44.46493928527515</v>
       </c>
       <c r="Q18" t="n">
-        <v>279</v>
+        <v>173.0792650904796</v>
       </c>
       <c r="R18" t="n">
         <v>279</v>
@@ -28873,10 +28873,10 @@
         <v>279</v>
       </c>
       <c r="H20" t="n">
-        <v>279</v>
+        <v>275.549808614586</v>
       </c>
       <c r="I20" t="n">
-        <v>146.6309682972706</v>
+        <v>150.0811596826846</v>
       </c>
       <c r="J20" t="n">
         <v>0</v>
@@ -28955,31 +28955,31 @@
         <v>279</v>
       </c>
       <c r="I21" t="n">
+        <v>217.1263858913485</v>
+      </c>
+      <c r="J21" t="n">
+        <v>0</v>
+      </c>
+      <c r="K21" t="n">
+        <v>0</v>
+      </c>
+      <c r="L21" t="n">
+        <v>0</v>
+      </c>
+      <c r="M21" t="n">
         <v>279</v>
       </c>
-      <c r="J21" t="n">
-        <v>0</v>
-      </c>
-      <c r="K21" t="n">
-        <v>0</v>
-      </c>
-      <c r="L21" t="n">
-        <v>0</v>
-      </c>
-      <c r="M21" t="n">
-        <v>0</v>
-      </c>
       <c r="N21" t="n">
-        <v>155.6705902671029</v>
+        <v>279</v>
       </c>
       <c r="O21" t="n">
         <v>0</v>
       </c>
       <c r="P21" t="n">
-        <v>279</v>
+        <v>44.46493928527515</v>
       </c>
       <c r="Q21" t="n">
-        <v>279</v>
+        <v>173.0792650904796</v>
       </c>
       <c r="R21" t="n">
         <v>279</v>
@@ -29107,13 +29107,13 @@
         <v>279</v>
       </c>
       <c r="G23" t="n">
-        <v>279</v>
+        <v>275.549808614586</v>
       </c>
       <c r="H23" t="n">
         <v>279</v>
       </c>
       <c r="I23" t="n">
-        <v>146.6309682972706</v>
+        <v>150.0811596826846</v>
       </c>
       <c r="J23" t="n">
         <v>0</v>
@@ -29195,28 +29195,28 @@
         <v>217.1263858913485</v>
       </c>
       <c r="J24" t="n">
-        <v>217.5442043757545</v>
+        <v>0</v>
       </c>
       <c r="K24" t="n">
+        <v>0</v>
+      </c>
+      <c r="L24" t="n">
         <v>279</v>
       </c>
-      <c r="L24" t="n">
-        <v>0</v>
-      </c>
       <c r="M24" t="n">
-        <v>0</v>
+        <v>44.46493928527474</v>
       </c>
       <c r="N24" t="n">
         <v>0</v>
       </c>
       <c r="O24" t="n">
-        <v>0</v>
+        <v>279</v>
       </c>
       <c r="P24" t="n">
         <v>0</v>
       </c>
       <c r="Q24" t="n">
-        <v>279</v>
+        <v>173.0792650904796</v>
       </c>
       <c r="R24" t="n">
         <v>279</v>
@@ -29438,7 +29438,7 @@
         <v>225</v>
       </c>
       <c r="L27" t="n">
-        <v>225</v>
+        <v>19.11687125883913</v>
       </c>
       <c r="M27" t="n">
         <v>225</v>
@@ -29450,7 +29450,7 @@
         <v>225</v>
       </c>
       <c r="P27" t="n">
-        <v>19.11687125883908</v>
+        <v>225</v>
       </c>
       <c r="Q27" t="n">
         <v>225</v>
@@ -29669,7 +29669,7 @@
         <v>251</v>
       </c>
       <c r="J30" t="n">
-        <v>251</v>
+        <v>244.1190264315979</v>
       </c>
       <c r="K30" t="n">
         <v>0</v>
@@ -29684,13 +29684,13 @@
         <v>251</v>
       </c>
       <c r="O30" t="n">
-        <v>166.1982915220774</v>
+        <v>251</v>
       </c>
       <c r="P30" t="n">
         <v>251</v>
       </c>
       <c r="Q30" t="n">
-        <v>251</v>
+        <v>173.0792650904796</v>
       </c>
       <c r="R30" t="n">
         <v>251</v>
@@ -29906,7 +29906,7 @@
         <v>217.1263858913485</v>
       </c>
       <c r="J33" t="n">
-        <v>0</v>
+        <v>176.7238924533193</v>
       </c>
       <c r="K33" t="n">
         <v>0</v>
@@ -29921,13 +29921,13 @@
         <v>0</v>
       </c>
       <c r="O33" t="n">
-        <v>61.80315754379833</v>
+        <v>0</v>
       </c>
       <c r="P33" t="n">
         <v>288</v>
       </c>
       <c r="Q33" t="n">
-        <v>288</v>
+        <v>173.0792650904796</v>
       </c>
       <c r="R33" t="n">
         <v>288</v>
@@ -30088,7 +30088,7 @@
         <v>0</v>
       </c>
       <c r="R35" t="n">
-        <v>250.8785988285853</v>
+        <v>250.8785988282945</v>
       </c>
       <c r="S35" t="n">
         <v>288</v>
@@ -30149,10 +30149,10 @@
         <v>0</v>
       </c>
       <c r="L36" t="n">
-        <v>0</v>
+        <v>176.723892453319</v>
       </c>
       <c r="M36" t="n">
-        <v>61.80315754379851</v>
+        <v>0</v>
       </c>
       <c r="N36" t="n">
         <v>0</v>
@@ -30164,7 +30164,7 @@
         <v>0</v>
       </c>
       <c r="Q36" t="n">
-        <v>288</v>
+        <v>173.0792650904796</v>
       </c>
       <c r="R36" t="n">
         <v>288</v>
@@ -30325,7 +30325,7 @@
         <v>0</v>
       </c>
       <c r="R38" t="n">
-        <v>250.8785988286734</v>
+        <v>250.8785988282945</v>
       </c>
       <c r="S38" t="n">
         <v>288</v>
@@ -30389,16 +30389,16 @@
         <v>0</v>
       </c>
       <c r="M39" t="n">
-        <v>0</v>
+        <v>176.7238924533193</v>
       </c>
       <c r="N39" t="n">
         <v>0</v>
       </c>
       <c r="O39" t="n">
+        <v>0</v>
+      </c>
+      <c r="P39" t="n">
         <v>288</v>
-      </c>
-      <c r="P39" t="n">
-        <v>176.7238924533191</v>
       </c>
       <c r="Q39" t="n">
         <v>173.0792650904796</v>
@@ -30620,7 +30620,7 @@
         <v>195</v>
       </c>
       <c r="K42" t="n">
-        <v>195</v>
+        <v>103.4446646606945</v>
       </c>
       <c r="L42" t="n">
         <v>195</v>
@@ -30629,7 +30629,7 @@
         <v>195</v>
       </c>
       <c r="N42" t="n">
-        <v>62.0200712105829</v>
+        <v>195</v>
       </c>
       <c r="O42" t="n">
         <v>195</v>
@@ -30638,7 +30638,7 @@
         <v>195</v>
       </c>
       <c r="Q42" t="n">
-        <v>195</v>
+        <v>173.0792650904796</v>
       </c>
       <c r="R42" t="n">
         <v>195</v>
@@ -30693,10 +30693,10 @@
         <v>195</v>
       </c>
       <c r="I43" t="n">
-        <v>195</v>
+        <v>176.6334556201183</v>
       </c>
       <c r="J43" t="n">
-        <v>58.91202791373284</v>
+        <v>86.86336426411265</v>
       </c>
       <c r="K43" t="n">
         <v>195</v>
@@ -30729,7 +30729,7 @@
         <v>195</v>
       </c>
       <c r="U43" t="n">
-        <v>195</v>
+        <v>150.9583912744579</v>
       </c>
       <c r="V43" t="n">
         <v>195</v>
@@ -30857,7 +30857,7 @@
         <v>115</v>
       </c>
       <c r="K45" t="n">
-        <v>115</v>
+        <v>56.41509433962264</v>
       </c>
       <c r="L45" t="n">
         <v>115</v>
@@ -30866,7 +30866,7 @@
         <v>0</v>
       </c>
       <c r="N45" t="n">
-        <v>101.5458780174107</v>
+        <v>115</v>
       </c>
       <c r="O45" t="n">
         <v>115</v>
@@ -30933,7 +30933,7 @@
         <v>115</v>
       </c>
       <c r="J46" t="n">
-        <v>35.26894883590776</v>
+        <v>115</v>
       </c>
       <c r="K46" t="n">
         <v>115</v>
@@ -34746,7 +34746,7 @@
         <v>815</v>
       </c>
       <c r="K2" t="n">
-        <v>783.0093003026275</v>
+        <v>783.0093003026375</v>
       </c>
       <c r="L2" t="n">
         <v>815</v>
@@ -34892,13 +34892,13 @@
         <v>125.6171440322581</v>
       </c>
       <c r="G4" t="n">
-        <v>154.95612715847</v>
+        <v>0</v>
       </c>
       <c r="H4" t="n">
         <v>171.2288738983814</v>
       </c>
       <c r="I4" t="n">
-        <v>223.3665443798817</v>
+        <v>0</v>
       </c>
       <c r="J4" t="n">
         <v>364.7310511640923</v>
@@ -34928,13 +34928,13 @@
         <v>0</v>
       </c>
       <c r="S4" t="n">
-        <v>37.62652029714457</v>
+        <v>0</v>
       </c>
       <c r="T4" t="n">
-        <v>44.41614984640352</v>
+        <v>189.9754334937423</v>
       </c>
       <c r="U4" t="n">
-        <v>0</v>
+        <v>157.8552610376198</v>
       </c>
       <c r="V4" t="n">
         <v>0</v>
@@ -34946,7 +34946,7 @@
         <v>0</v>
       </c>
       <c r="Y4" t="n">
-        <v>0</v>
+        <v>112.5346471505376</v>
       </c>
     </row>
     <row r="5">
@@ -34992,7 +34992,7 @@
         <v>815</v>
       </c>
       <c r="N5" t="n">
-        <v>783.0093003026433</v>
+        <v>783.0093003026349</v>
       </c>
       <c r="O5" t="n">
         <v>815</v>
@@ -35114,22 +35114,22 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>0</v>
+        <v>112.8861996629213</v>
       </c>
       <c r="C7" t="n">
         <v>0</v>
       </c>
       <c r="D7" t="n">
-        <v>114.4637819444445</v>
+        <v>0</v>
       </c>
       <c r="E7" t="n">
         <v>119.0190951630435</v>
       </c>
       <c r="F7" t="n">
-        <v>125.6171440322581</v>
+        <v>0</v>
       </c>
       <c r="G7" t="n">
-        <v>154.95612715847</v>
+        <v>110.9135810340883</v>
       </c>
       <c r="H7" t="n">
         <v>171.2288738983814</v>
@@ -35168,22 +35168,22 @@
         <v>37.62652029714457</v>
       </c>
       <c r="T7" t="n">
-        <v>189.9754334937423</v>
+        <v>0</v>
       </c>
       <c r="U7" t="n">
-        <v>249.0416087255421</v>
+        <v>0</v>
       </c>
       <c r="V7" t="n">
-        <v>29.29356700805687</v>
+        <v>200.8296897837838</v>
       </c>
       <c r="W7" t="n">
-        <v>0</v>
+        <v>173.6271901612903</v>
       </c>
       <c r="X7" t="n">
-        <v>0</v>
+        <v>152.5563545698924</v>
       </c>
       <c r="Y7" t="n">
-        <v>0</v>
+        <v>112.5346471505376</v>
       </c>
     </row>
     <row r="8">
@@ -35220,7 +35220,7 @@
         <v>815</v>
       </c>
       <c r="K8" t="n">
-        <v>783.0093003026544</v>
+        <v>783.0093003026486</v>
       </c>
       <c r="L8" t="n">
         <v>815</v>
@@ -35351,31 +35351,31 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>112.8861996629213</v>
+        <v>0</v>
       </c>
       <c r="C10" t="n">
         <v>127.2747533519553</v>
       </c>
       <c r="D10" t="n">
-        <v>114.4637819444445</v>
+        <v>68.03184104952365</v>
       </c>
       <c r="E10" t="n">
-        <v>119.0190951630435</v>
+        <v>0</v>
       </c>
       <c r="F10" t="n">
-        <v>125.6171440322581</v>
+        <v>0</v>
       </c>
       <c r="G10" t="n">
-        <v>154.95612715847</v>
+        <v>0</v>
       </c>
       <c r="H10" t="n">
-        <v>171.2288738983814</v>
+        <v>0</v>
       </c>
       <c r="I10" t="n">
-        <v>223.3665443798817</v>
+        <v>0</v>
       </c>
       <c r="J10" t="n">
-        <v>0</v>
+        <v>364.7310511640923</v>
       </c>
       <c r="K10" t="n">
         <v>0</v>
@@ -35408,19 +35408,19 @@
         <v>189.9754334937423</v>
       </c>
       <c r="U10" t="n">
-        <v>74.74532206418613</v>
+        <v>249.0416087255421</v>
       </c>
       <c r="V10" t="n">
-        <v>0</v>
+        <v>200.8296897837838</v>
       </c>
       <c r="W10" t="n">
-        <v>0</v>
+        <v>173.6271901612903</v>
       </c>
       <c r="X10" t="n">
-        <v>0</v>
+        <v>152.5563545698924</v>
       </c>
       <c r="Y10" t="n">
-        <v>112.5346471505376</v>
+        <v>0</v>
       </c>
     </row>
     <row r="11">
@@ -35457,19 +35457,19 @@
         <v>395.2617303410664</v>
       </c>
       <c r="K11" t="n">
-        <v>716.8751175230996</v>
+        <v>0</v>
       </c>
       <c r="L11" t="n">
+        <v>685.8000588216257</v>
+      </c>
+      <c r="M11" t="n">
+        <v>516.0089179080152</v>
+      </c>
+      <c r="N11" t="n">
+        <v>0</v>
+      </c>
+      <c r="O11" t="n">
         <v>815</v>
-      </c>
-      <c r="M11" t="n">
-        <v>484.9338592065413</v>
-      </c>
-      <c r="N11" t="n">
-        <v>0</v>
-      </c>
-      <c r="O11" t="n">
-        <v>0</v>
       </c>
       <c r="P11" t="n">
         <v>815</v>
@@ -35548,10 +35548,10 @@
         <v>359.6265501086548</v>
       </c>
       <c r="O12" t="n">
-        <v>466.4570219027464</v>
+        <v>260.5738931615856</v>
       </c>
       <c r="P12" t="n">
-        <v>132.7828757734923</v>
+        <v>338.6660045146532</v>
       </c>
       <c r="Q12" t="n">
         <v>51.92073490952041</v>
@@ -35691,13 +35691,13 @@
         <v>0</v>
       </c>
       <c r="J14" t="n">
-        <v>395.2617303410664</v>
+        <v>0</v>
       </c>
       <c r="K14" t="n">
-        <v>716.8751175230996</v>
+        <v>716.8751175230994</v>
       </c>
       <c r="L14" t="n">
-        <v>815</v>
+        <v>0</v>
       </c>
       <c r="M14" t="n">
         <v>516.0089179080152</v>
@@ -35706,13 +35706,13 @@
         <v>619.4144644189528</v>
       </c>
       <c r="O14" t="n">
-        <v>0</v>
+        <v>116.7428182785516</v>
       </c>
       <c r="P14" t="n">
-        <v>0</v>
+        <v>815</v>
       </c>
       <c r="Q14" t="n">
-        <v>164.5104768795733</v>
+        <v>443.0293889420883</v>
       </c>
       <c r="R14" t="n">
         <v>0</v>
@@ -35767,22 +35767,22 @@
         <v>0</v>
       </c>
       <c r="I15" t="n">
-        <v>61.87361410865147</v>
+        <v>0</v>
       </c>
       <c r="J15" t="n">
-        <v>280.8791965047787</v>
+        <v>125.2086062376757</v>
       </c>
       <c r="K15" t="n">
-        <v>191.1038546407913</v>
+        <v>470.1038546407913</v>
       </c>
       <c r="L15" t="n">
         <v>274.091375348687</v>
       </c>
       <c r="M15" t="n">
-        <v>86.95004216450428</v>
+        <v>365.9500421645043</v>
       </c>
       <c r="N15" t="n">
-        <v>413.6265501086548</v>
+        <v>179.0914893939298</v>
       </c>
       <c r="O15" t="n">
         <v>241.4570219027464</v>
@@ -35791,7 +35791,7 @@
         <v>113.6660045146532</v>
       </c>
       <c r="Q15" t="n">
-        <v>105.9207349095204</v>
+        <v>0</v>
       </c>
       <c r="R15" t="n">
         <v>0</v>
@@ -35934,13 +35934,13 @@
         <v>716.8751175230996</v>
       </c>
       <c r="L17" t="n">
-        <v>815</v>
+        <v>536.481087937485</v>
       </c>
       <c r="M17" t="n">
         <v>516.0089179080152</v>
       </c>
       <c r="N17" t="n">
-        <v>340.8955523564375</v>
+        <v>619.4144644189528</v>
       </c>
       <c r="O17" t="n">
         <v>0</v>
@@ -36004,13 +36004,13 @@
         <v>0</v>
       </c>
       <c r="I18" t="n">
-        <v>61.87361410865147</v>
+        <v>0</v>
       </c>
       <c r="J18" t="n">
         <v>404.2086062376757</v>
       </c>
       <c r="K18" t="n">
-        <v>346.7744449078943</v>
+        <v>191.1038546407913</v>
       </c>
       <c r="L18" t="n">
         <v>274.091375348687</v>
@@ -36022,13 +36022,13 @@
         <v>134.6265501086548</v>
       </c>
       <c r="O18" t="n">
-        <v>241.4570219027464</v>
+        <v>520.4570219027464</v>
       </c>
       <c r="P18" t="n">
-        <v>113.6660045146532</v>
+        <v>158.1309437999284</v>
       </c>
       <c r="Q18" t="n">
-        <v>105.9207349095204</v>
+        <v>0</v>
       </c>
       <c r="R18" t="n">
         <v>0</v>
@@ -36165,25 +36165,25 @@
         <v>0</v>
       </c>
       <c r="J20" t="n">
-        <v>116.7428182785515</v>
+        <v>0</v>
       </c>
       <c r="K20" t="n">
         <v>716.8751175230994</v>
       </c>
       <c r="L20" t="n">
-        <v>815</v>
+        <v>0</v>
       </c>
       <c r="M20" t="n">
-        <v>516.0089179080152</v>
+        <v>0</v>
       </c>
       <c r="N20" t="n">
         <v>619.4144644189528</v>
       </c>
       <c r="O20" t="n">
-        <v>0</v>
+        <v>815</v>
       </c>
       <c r="P20" t="n">
-        <v>0</v>
+        <v>632.7517361865665</v>
       </c>
       <c r="Q20" t="n">
         <v>443.0293889420883</v>
@@ -36241,7 +36241,7 @@
         <v>0</v>
       </c>
       <c r="I21" t="n">
-        <v>61.87361410865147</v>
+        <v>0</v>
       </c>
       <c r="J21" t="n">
         <v>125.2086062376757</v>
@@ -36253,19 +36253,19 @@
         <v>274.091375348687</v>
       </c>
       <c r="M21" t="n">
-        <v>86.95004216450428</v>
+        <v>365.9500421645043</v>
       </c>
       <c r="N21" t="n">
-        <v>290.2971403757577</v>
+        <v>413.6265501086548</v>
       </c>
       <c r="O21" t="n">
         <v>241.4570219027464</v>
       </c>
       <c r="P21" t="n">
-        <v>392.6660045146532</v>
+        <v>158.1309437999284</v>
       </c>
       <c r="Q21" t="n">
-        <v>105.9207349095204</v>
+        <v>0</v>
       </c>
       <c r="R21" t="n">
         <v>0</v>
@@ -36408,22 +36408,22 @@
         <v>716.8751175230996</v>
       </c>
       <c r="L23" t="n">
-        <v>536.481087937485</v>
+        <v>815</v>
       </c>
       <c r="M23" t="n">
-        <v>516.0089179080152</v>
+        <v>0</v>
       </c>
       <c r="N23" t="n">
         <v>619.4144644189528</v>
       </c>
       <c r="O23" t="n">
-        <v>0</v>
+        <v>680.5193947875886</v>
       </c>
       <c r="P23" t="n">
         <v>0</v>
       </c>
       <c r="Q23" t="n">
-        <v>443.0293889420883</v>
+        <v>0</v>
       </c>
       <c r="R23" t="n">
         <v>0</v>
@@ -36481,28 +36481,28 @@
         <v>0</v>
       </c>
       <c r="J24" t="n">
-        <v>342.7528106134302</v>
+        <v>125.2086062376757</v>
       </c>
       <c r="K24" t="n">
-        <v>470.1038546407913</v>
+        <v>191.1038546407913</v>
       </c>
       <c r="L24" t="n">
-        <v>274.091375348687</v>
+        <v>553.0913753486871</v>
       </c>
       <c r="M24" t="n">
-        <v>86.95004216450428</v>
+        <v>131.414981449779</v>
       </c>
       <c r="N24" t="n">
         <v>134.6265501086548</v>
       </c>
       <c r="O24" t="n">
-        <v>241.4570219027464</v>
+        <v>520.4570219027464</v>
       </c>
       <c r="P24" t="n">
         <v>113.6660045146532</v>
       </c>
       <c r="Q24" t="n">
-        <v>105.9207349095204</v>
+        <v>0</v>
       </c>
       <c r="R24" t="n">
         <v>0</v>
@@ -36639,25 +36639,25 @@
         <v>0</v>
       </c>
       <c r="J26" t="n">
-        <v>395.2617303410664</v>
+        <v>0</v>
       </c>
       <c r="K26" t="n">
         <v>0</v>
       </c>
       <c r="L26" t="n">
-        <v>0</v>
+        <v>779</v>
       </c>
       <c r="M26" t="n">
         <v>516.0089179080152</v>
       </c>
       <c r="N26" t="n">
-        <v>619.4144644189528</v>
+        <v>0</v>
       </c>
       <c r="O26" t="n">
-        <v>779.0000000000257</v>
+        <v>567.4869456751491</v>
       </c>
       <c r="P26" t="n">
-        <v>331.8107509151041</v>
+        <v>779</v>
       </c>
       <c r="Q26" t="n">
         <v>443.0293889420883</v>
@@ -36724,7 +36724,7 @@
         <v>416.1038546407913</v>
       </c>
       <c r="L27" t="n">
-        <v>499.091375348687</v>
+        <v>293.2082466075261</v>
       </c>
       <c r="M27" t="n">
         <v>311.9500421645043</v>
@@ -36736,7 +36736,7 @@
         <v>466.4570219027464</v>
       </c>
       <c r="P27" t="n">
-        <v>132.7828757734923</v>
+        <v>338.6660045146532</v>
       </c>
       <c r="Q27" t="n">
         <v>51.92073490952041</v>
@@ -36879,22 +36879,22 @@
         <v>395.2617303410664</v>
       </c>
       <c r="K29" t="n">
-        <v>0</v>
+        <v>716.8751175230996</v>
       </c>
       <c r="L29" t="n">
         <v>0</v>
       </c>
       <c r="M29" t="n">
-        <v>516.0089179080152</v>
+        <v>130.9445513000456</v>
       </c>
       <c r="N29" t="n">
-        <v>172.2252153340173</v>
+        <v>619.4144644189528</v>
       </c>
       <c r="O29" t="n">
-        <v>779.0000000000325</v>
+        <v>779</v>
       </c>
       <c r="P29" t="n">
-        <v>779.0000000000325</v>
+        <v>0</v>
       </c>
       <c r="Q29" t="n">
         <v>443.0293889420883</v>
@@ -36955,7 +36955,7 @@
         <v>33.87361410865147</v>
       </c>
       <c r="J30" t="n">
-        <v>376.2086062376757</v>
+        <v>369.3276326692737</v>
       </c>
       <c r="K30" t="n">
         <v>191.1038546407913</v>
@@ -36970,13 +36970,13 @@
         <v>385.6265501086548</v>
       </c>
       <c r="O30" t="n">
-        <v>407.6553134248237</v>
+        <v>492.4570219027464</v>
       </c>
       <c r="P30" t="n">
         <v>364.6660045146532</v>
       </c>
       <c r="Q30" t="n">
-        <v>77.92073490952041</v>
+        <v>0</v>
       </c>
       <c r="R30" t="n">
         <v>0</v>
@@ -37119,22 +37119,22 @@
         <v>716.8751175230994</v>
       </c>
       <c r="L32" t="n">
-        <v>575.0162209571616</v>
+        <v>778.9999999999999</v>
       </c>
       <c r="M32" t="n">
-        <v>0</v>
+        <v>516.0089179080152</v>
       </c>
       <c r="N32" t="n">
-        <v>619.4144644189528</v>
+        <v>0</v>
       </c>
       <c r="O32" t="n">
-        <v>779.0000000000466</v>
+        <v>0</v>
       </c>
       <c r="P32" t="n">
-        <v>0</v>
+        <v>779</v>
       </c>
       <c r="Q32" t="n">
-        <v>443.0293889420883</v>
+        <v>342.4511564102376</v>
       </c>
       <c r="R32" t="n">
         <v>0</v>
@@ -37192,7 +37192,7 @@
         <v>0</v>
       </c>
       <c r="J33" t="n">
-        <v>125.2086062376757</v>
+        <v>301.932498690995</v>
       </c>
       <c r="K33" t="n">
         <v>191.1038546407913</v>
@@ -37207,13 +37207,13 @@
         <v>134.6265501086548</v>
       </c>
       <c r="O33" t="n">
-        <v>303.2601794465447</v>
+        <v>241.4570219027464</v>
       </c>
       <c r="P33" t="n">
         <v>401.6660045146532</v>
       </c>
       <c r="Q33" t="n">
-        <v>114.9207349095204</v>
+        <v>0</v>
       </c>
       <c r="R33" t="n">
         <v>0</v>
@@ -37353,28 +37353,28 @@
         <v>395.2617303410664</v>
       </c>
       <c r="K35" t="n">
-        <v>0</v>
+        <v>716.8751175230996</v>
       </c>
       <c r="L35" t="n">
-        <v>0</v>
+        <v>463.1983439771709</v>
       </c>
       <c r="M35" t="n">
-        <v>516.0089179080152</v>
+        <v>0</v>
       </c>
       <c r="N35" t="n">
-        <v>667.2530859522192</v>
+        <v>0</v>
       </c>
       <c r="O35" t="n">
-        <v>332.7820687076439</v>
+        <v>779</v>
       </c>
       <c r="P35" t="n">
-        <v>779.0000000000703</v>
+        <v>779</v>
       </c>
       <c r="Q35" t="n">
-        <v>443.0293889420883</v>
+        <v>0</v>
       </c>
       <c r="R35" t="n">
-        <v>2.907627001122543e-10</v>
+        <v>0</v>
       </c>
       <c r="S35" t="n">
         <v>0</v>
@@ -37435,10 +37435,10 @@
         <v>191.1038546407913</v>
       </c>
       <c r="L36" t="n">
-        <v>274.091375348687</v>
+        <v>450.815267802006</v>
       </c>
       <c r="M36" t="n">
-        <v>148.7531997083028</v>
+        <v>86.95004216450428</v>
       </c>
       <c r="N36" t="n">
         <v>134.6265501086548</v>
@@ -37450,7 +37450,7 @@
         <v>113.6660045146532</v>
       </c>
       <c r="Q36" t="n">
-        <v>114.9207349095204</v>
+        <v>0</v>
       </c>
       <c r="R36" t="n">
         <v>0</v>
@@ -37590,7 +37590,7 @@
         <v>395.2617303410664</v>
       </c>
       <c r="K38" t="n">
-        <v>737.0440725707859</v>
+        <v>764.7137390468558</v>
       </c>
       <c r="L38" t="n">
         <v>779</v>
@@ -37602,7 +37602,7 @@
         <v>0</v>
       </c>
       <c r="O38" t="n">
-        <v>779.0000000000921</v>
+        <v>751.3303335113899</v>
       </c>
       <c r="P38" t="n">
         <v>0</v>
@@ -37611,7 +37611,7 @@
         <v>443.0293889420883</v>
       </c>
       <c r="R38" t="n">
-        <v>3.789561257387201e-10</v>
+        <v>0</v>
       </c>
       <c r="S38" t="n">
         <v>0</v>
@@ -37675,16 +37675,16 @@
         <v>274.091375348687</v>
       </c>
       <c r="M39" t="n">
-        <v>86.95004216450428</v>
+        <v>263.6739346178235</v>
       </c>
       <c r="N39" t="n">
         <v>134.6265501086548</v>
       </c>
       <c r="O39" t="n">
-        <v>529.4570219027464</v>
+        <v>241.4570219027464</v>
       </c>
       <c r="P39" t="n">
-        <v>290.3898969679723</v>
+        <v>401.6660045146532</v>
       </c>
       <c r="Q39" t="n">
         <v>0</v>
@@ -37827,22 +37827,22 @@
         <v>0</v>
       </c>
       <c r="K41" t="n">
-        <v>567.4869456748687</v>
+        <v>716.8751175230994</v>
       </c>
       <c r="L41" t="n">
-        <v>0</v>
+        <v>778.9999999999999</v>
       </c>
       <c r="M41" t="n">
-        <v>516.0089179080152</v>
+        <v>0</v>
       </c>
       <c r="N41" t="n">
-        <v>0</v>
+        <v>619.4144644189528</v>
       </c>
       <c r="O41" t="n">
-        <v>779.0000000001403</v>
+        <v>526.2062816411119</v>
       </c>
       <c r="P41" t="n">
-        <v>779.0000000001403</v>
+        <v>0</v>
       </c>
       <c r="Q41" t="n">
         <v>443.0293889420883</v>
@@ -37906,7 +37906,7 @@
         <v>320.2086062376757</v>
       </c>
       <c r="K42" t="n">
-        <v>386.1038546407913</v>
+        <v>294.5485193014858</v>
       </c>
       <c r="L42" t="n">
         <v>469.091375348687</v>
@@ -37915,7 +37915,7 @@
         <v>281.9500421645043</v>
       </c>
       <c r="N42" t="n">
-        <v>196.6466213192377</v>
+        <v>329.6265501086548</v>
       </c>
       <c r="O42" t="n">
         <v>436.4570219027464</v>
@@ -37924,7 +37924,7 @@
         <v>308.6660045146532</v>
       </c>
       <c r="Q42" t="n">
-        <v>21.92073490952041</v>
+        <v>0</v>
       </c>
       <c r="R42" t="n">
         <v>0</v>
@@ -37979,10 +37979,10 @@
         <v>0</v>
       </c>
       <c r="I43" t="n">
-        <v>18.36654437988173</v>
+        <v>0</v>
       </c>
       <c r="J43" t="n">
-        <v>23.64307907782507</v>
+        <v>51.59441542820487</v>
       </c>
       <c r="K43" t="n">
         <v>0</v>
@@ -38015,7 +38015,7 @@
         <v>0</v>
       </c>
       <c r="U43" t="n">
-        <v>44.04160872554206</v>
+        <v>0</v>
       </c>
       <c r="V43" t="n">
         <v>0</v>
@@ -38061,25 +38061,25 @@
         <v>0</v>
       </c>
       <c r="J44" t="n">
-        <v>395.2617303410664</v>
+        <v>0</v>
       </c>
       <c r="K44" t="n">
-        <v>0</v>
+        <v>716.8751175230994</v>
       </c>
       <c r="L44" t="n">
-        <v>0</v>
+        <v>778.9999999999999</v>
       </c>
       <c r="M44" t="n">
         <v>516.0089179080152</v>
       </c>
       <c r="N44" t="n">
-        <v>619.4144644189528</v>
+        <v>293.641217094138</v>
       </c>
       <c r="O44" t="n">
-        <v>774.8401398570225</v>
+        <v>0</v>
       </c>
       <c r="P44" t="n">
-        <v>779.0000000001958</v>
+        <v>779</v>
       </c>
       <c r="Q44" t="n">
         <v>0</v>
@@ -38143,7 +38143,7 @@
         <v>240.2086062376757</v>
       </c>
       <c r="K45" t="n">
-        <v>306.1038546407913</v>
+        <v>247.5189489804139</v>
       </c>
       <c r="L45" t="n">
         <v>389.091375348687</v>
@@ -38152,7 +38152,7 @@
         <v>86.95004216450428</v>
       </c>
       <c r="N45" t="n">
-        <v>236.1724281260655</v>
+        <v>249.6265501086548</v>
       </c>
       <c r="O45" t="n">
         <v>356.4570219027464</v>
@@ -38219,7 +38219,7 @@
         <v>0</v>
       </c>
       <c r="J46" t="n">
-        <v>0</v>
+        <v>79.73105116409224</v>
       </c>
       <c r="K46" t="n">
         <v>0</v>
